--- a/exames.xlsx
+++ b/exames.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence - testes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6FA4BF8-C457-4937-AF88-3E64B6BF2B62}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C6AEA07-D1BD-4688-B133-157330371A00}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="59">
   <si>
     <t/>
   </si>
@@ -176,6 +176,30 @@
   </si>
   <si>
     <t>b93caca5-b4fb-4459-bb9f-da4d67daa626</t>
+  </si>
+  <si>
+    <t>EDISON NEVES</t>
+  </si>
+  <si>
+    <t>edison.neves@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>POA</t>
+  </si>
+  <si>
+    <t>Avaliação Modular - Contabilidade Digital II</t>
+  </si>
+  <si>
+    <t>c0394b5e-9777-4f5c-8937-09f20b29b796</t>
+  </si>
+  <si>
+    <t>0db85fb7-71ed-473e-adc1-e990d45c178d</t>
+  </si>
+  <si>
+    <t>Avaliação modular - Contabilidade Digital I</t>
+  </si>
+  <si>
+    <t>63dff9f6-a542-43d5-a690-98df0e2dc15b</t>
   </si>
 </sst>
 </file>
@@ -624,58 +648,58 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="B2">
-        <v>7031896</v>
+        <v>3377344</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
         <v>31</v>
       </c>
       <c r="H2" s="1"/>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L2">
-        <v>1706681</v>
+        <v>1724163</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="N2" s="2">
-        <v>46218</v>
+        <v>46237</v>
       </c>
       <c r="O2" s="2">
-        <v>46218</v>
+        <v>46237</v>
       </c>
       <c r="P2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Q2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="S2" t="s">
         <v>20</v>
       </c>
       <c r="T2">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B3">
         <v>7031896</v>
@@ -697,36 +721,36 @@
         <v>24</v>
       </c>
       <c r="L3">
-        <v>1715169</v>
+        <v>1706681</v>
       </c>
       <c r="M3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N3" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="O3" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="P3">
         <v>83</v>
       </c>
       <c r="Q3" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S3" t="s">
         <v>20</v>
       </c>
       <c r="T3">
-        <v>117</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B4">
         <v>7031896</v>
@@ -748,16 +772,16 @@
         <v>24</v>
       </c>
       <c r="L4">
-        <v>1711329</v>
+        <v>1724163</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="N4" s="2">
-        <v>46213</v>
+        <v>46238</v>
       </c>
       <c r="O4" s="2">
-        <v>46213</v>
+        <v>46238</v>
       </c>
       <c r="P4">
         <v>90</v>
@@ -766,18 +790,18 @@
         <v>20</v>
       </c>
       <c r="R4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="S4" t="s">
         <v>20</v>
       </c>
       <c r="T4">
-        <v>31</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B5">
         <v>7031896</v>
@@ -799,36 +823,36 @@
         <v>24</v>
       </c>
       <c r="L5">
-        <v>1708464</v>
+        <v>1711329</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="N5" s="2">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="O5" s="2">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="P5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="s">
         <v>20</v>
       </c>
       <c r="R5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="S5" t="s">
         <v>20</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6">
         <v>7031896</v>
@@ -879,19 +903,19 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>7031895</v>
+        <v>7031896</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
@@ -913,36 +937,36 @@
         <v>46211</v>
       </c>
       <c r="P7">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="s">
         <v>20</v>
       </c>
       <c r="R7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S7" t="s">
         <v>20</v>
       </c>
       <c r="T7">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B8">
-        <v>7031895</v>
+        <v>7031896</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
@@ -958,10 +982,10 @@
         <v>45</v>
       </c>
       <c r="N8" s="2">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="O8" s="2">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="P8">
         <v>83</v>
@@ -970,18 +994,18 @@
         <v>20</v>
       </c>
       <c r="R8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S8" t="s">
         <v>20</v>
       </c>
       <c r="T8">
-        <v>1028</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B9">
         <v>7031895</v>
@@ -1003,36 +1027,36 @@
         <v>24</v>
       </c>
       <c r="L9">
-        <v>1706681</v>
+        <v>1711329</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N9" s="2">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="O9" s="2">
-        <v>46218</v>
+        <v>46213</v>
       </c>
       <c r="P9">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="S9" t="s">
         <v>20</v>
       </c>
       <c r="T9">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B10">
         <v>7031895</v>
@@ -1054,36 +1078,36 @@
         <v>24</v>
       </c>
       <c r="L10">
-        <v>1711329</v>
+        <v>1715169</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N10" s="2">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="O10" s="2">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="Q10" t="s">
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="S10" t="s">
         <v>20</v>
       </c>
       <c r="T10">
-        <v>30</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B11">
         <v>7031895</v>
@@ -1134,77 +1158,77 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>324</v>
+        <v>155</v>
       </c>
       <c r="B12">
-        <v>7031897</v>
+        <v>7031895</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
         <v>31</v>
       </c>
       <c r="H12" s="1"/>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L12">
-        <v>1710979</v>
+        <v>1706681</v>
       </c>
       <c r="M12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N12" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O12" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="Q12" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="R12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="S12" t="s">
         <v>20</v>
       </c>
       <c r="T12">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>325</v>
+        <v>156</v>
       </c>
       <c r="B13">
-        <v>7031897</v>
+        <v>7031895</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
         <v>31</v>
       </c>
       <c r="H13" s="1"/>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L13">
         <v>1708464</v>
@@ -1219,24 +1243,24 @@
         <v>46211</v>
       </c>
       <c r="P13">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="s">
         <v>20</v>
       </c>
       <c r="R13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S13" t="s">
         <v>20</v>
       </c>
       <c r="T13">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B14">
         <v>7031897</v>
@@ -1258,36 +1282,36 @@
         <v>32</v>
       </c>
       <c r="L14">
-        <v>1715169</v>
+        <v>1711329</v>
       </c>
       <c r="M14" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="N14" s="2">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="O14" s="2">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="P14">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="Q14" t="s">
         <v>20</v>
       </c>
       <c r="R14" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="S14" t="s">
         <v>20</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B15">
         <v>7031897</v>
@@ -1321,24 +1345,24 @@
         <v>46217</v>
       </c>
       <c r="P15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R15" t="s">
         <v>49</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B16">
         <v>7031897</v>
@@ -1360,36 +1384,36 @@
         <v>32</v>
       </c>
       <c r="L16">
-        <v>1711329</v>
+        <v>1723203</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="N16" s="2">
-        <v>46213</v>
+        <v>46237</v>
       </c>
       <c r="O16" s="2">
-        <v>46213</v>
+        <v>46237</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="s">
         <v>20</v>
       </c>
       <c r="R16" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="S16" t="s">
         <v>20</v>
       </c>
       <c r="T16">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B17">
         <v>7031897</v>
@@ -1411,47 +1435,185 @@
         <v>32</v>
       </c>
       <c r="L17">
+        <v>1715169</v>
+      </c>
+      <c r="M17" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" s="2">
+        <v>46217</v>
+      </c>
+      <c r="O17" s="2">
+        <v>46217</v>
+      </c>
+      <c r="P17">
+        <v>50</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>43</v>
+      </c>
+      <c r="R17" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" t="s">
+        <v>43</v>
+      </c>
+      <c r="T17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>334</v>
+      </c>
+      <c r="B18">
+        <v>7031897</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18">
+        <v>1708464</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="2">
+        <v>46211</v>
+      </c>
+      <c r="O18" s="2">
+        <v>46211</v>
+      </c>
+      <c r="P18">
+        <v>70</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>20</v>
+      </c>
+      <c r="R18" t="s">
+        <v>33</v>
+      </c>
+      <c r="S18" t="s">
+        <v>20</v>
+      </c>
+      <c r="T18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>335</v>
+      </c>
+      <c r="B19">
+        <v>7031897</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19">
         <v>1706681</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M19" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N19" s="2">
         <v>46218</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O19" s="2">
         <v>46218</v>
       </c>
-      <c r="P17">
+      <c r="P19">
         <v>83</v>
       </c>
-      <c r="Q17" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="Q19" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" t="s">
         <v>50</v>
       </c>
-      <c r="S17" t="s">
-        <v>20</v>
-      </c>
-      <c r="T17">
+      <c r="S19" t="s">
+        <v>20</v>
+      </c>
+      <c r="T19">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H18" s="1"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H19" s="1"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-    </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>336</v>
+      </c>
+      <c r="B20">
+        <v>7031897</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
       <c r="H20" s="1"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20">
+        <v>1710979</v>
+      </c>
+      <c r="M20" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" s="2">
+        <v>46216</v>
+      </c>
+      <c r="O20" s="2">
+        <v>46216</v>
+      </c>
+      <c r="P20">
+        <v>100</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" t="s">
+        <v>41</v>
+      </c>
+      <c r="S20" t="s">
+        <v>20</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H21" s="1"/>

--- a/exames.xlsx
+++ b/exames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C6AEA07-D1BD-4688-B133-157330371A00}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA382575-B11E-4EAC-9EE2-CBBBE116FA0F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$T$345</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="65">
   <si>
     <t/>
   </si>
@@ -200,6 +200,24 @@
   </si>
   <si>
     <t>63dff9f6-a542-43d5-a690-98df0e2dc15b</t>
+  </si>
+  <si>
+    <t>ANDERSON ANELLI</t>
+  </si>
+  <si>
+    <t>andersonanelli.anelli@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>Avaliação Modular - Contabilidade Digital III</t>
+  </si>
+  <si>
+    <t>5ff341a4-81c8-4584-8e9e-48f5b90ee8af</t>
+  </si>
+  <si>
+    <t>46d21eb7-dde8-4007-b693-7428cc05b0a9</t>
+  </si>
+  <si>
+    <t>2f8f76a1-e71d-43b2-ab6f-835104bf2b1b</t>
   </si>
 </sst>
 </file>
@@ -648,19 +666,19 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="B2">
-        <v>3377344</v>
+        <v>3394166</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
         <v>31</v>
@@ -670,87 +688,87 @@
         <v>53</v>
       </c>
       <c r="L2">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N2" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="O2" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="P2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q2" t="s">
         <v>20</v>
       </c>
       <c r="R2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="S2" t="s">
         <v>20</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B3">
-        <v>7031896</v>
+        <v>3377344</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="1"/>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L3">
-        <v>1706681</v>
+        <v>1724163</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="N3" s="2">
-        <v>46218</v>
+        <v>46237</v>
       </c>
       <c r="O3" s="2">
-        <v>46218</v>
+        <v>46237</v>
       </c>
       <c r="P3">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Q3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="S3" t="s">
         <v>20</v>
       </c>
       <c r="T3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B4">
         <v>7031896</v>
@@ -772,16 +790,16 @@
         <v>24</v>
       </c>
       <c r="L4">
-        <v>1724163</v>
+        <v>1711329</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N4" s="2">
-        <v>46238</v>
+        <v>46213</v>
       </c>
       <c r="O4" s="2">
-        <v>46238</v>
+        <v>46213</v>
       </c>
       <c r="P4">
         <v>90</v>
@@ -790,18 +808,18 @@
         <v>20</v>
       </c>
       <c r="R4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="S4" t="s">
         <v>20</v>
       </c>
       <c r="T4">
-        <v>1042</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B5">
         <v>7031896</v>
@@ -823,36 +841,36 @@
         <v>24</v>
       </c>
       <c r="L5">
-        <v>1711329</v>
+        <v>1706681</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N5" s="2">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="O5" s="2">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="Q5" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="R5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S5" t="s">
         <v>20</v>
       </c>
       <c r="T5">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B6">
         <v>7031896</v>
@@ -874,36 +892,36 @@
         <v>24</v>
       </c>
       <c r="L6">
-        <v>1710979</v>
+        <v>1715169</v>
       </c>
       <c r="M6" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="N6" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="O6" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="Q6" t="s">
         <v>20</v>
       </c>
       <c r="R6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
         <v>20</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B7">
         <v>7031896</v>
@@ -925,36 +943,36 @@
         <v>24</v>
       </c>
       <c r="L7">
-        <v>1708464</v>
+        <v>1724163</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="N7" s="2">
-        <v>46211</v>
+        <v>46238</v>
       </c>
       <c r="O7" s="2">
-        <v>46211</v>
+        <v>46238</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="s">
         <v>20</v>
       </c>
       <c r="R7" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="S7" t="s">
         <v>20</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B8">
         <v>7031896</v>
@@ -976,48 +994,48 @@
         <v>24</v>
       </c>
       <c r="L8">
-        <v>1715169</v>
+        <v>1708464</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="N8" s="2">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="O8" s="2">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="P8">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="s">
         <v>20</v>
       </c>
       <c r="R8" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="S8" t="s">
         <v>20</v>
       </c>
       <c r="T8">
-        <v>117</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B9">
-        <v>7031895</v>
+        <v>7031896</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
@@ -1027,16 +1045,16 @@
         <v>24</v>
       </c>
       <c r="L9">
-        <v>1711329</v>
+        <v>1710979</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N9" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="O9" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -1045,18 +1063,18 @@
         <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S9" t="s">
         <v>20</v>
       </c>
       <c r="T9">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B10">
         <v>7031895</v>
@@ -1078,36 +1096,36 @@
         <v>24</v>
       </c>
       <c r="L10">
-        <v>1715169</v>
+        <v>1724163</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="N10" s="2">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="O10" s="2">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="P10">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Q10" t="s">
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="S10" t="s">
         <v>20</v>
       </c>
       <c r="T10">
-        <v>1028</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B11">
         <v>7031895</v>
@@ -1158,7 +1176,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B12">
         <v>7031895</v>
@@ -1186,30 +1204,30 @@
         <v>42</v>
       </c>
       <c r="N12" s="2">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="O12" s="2">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="P12">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="Q12" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R12" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="S12" t="s">
         <v>20</v>
       </c>
       <c r="T12">
-        <v>20</v>
+        <v>28480</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B13">
         <v>7031895</v>
@@ -1231,189 +1249,189 @@
         <v>24</v>
       </c>
       <c r="L13">
-        <v>1708464</v>
+        <v>1711329</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="N13" s="2">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="O13" s="2">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="P13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="s">
         <v>20</v>
       </c>
       <c r="R13" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="S13" t="s">
         <v>20</v>
       </c>
       <c r="T13">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="B14">
-        <v>7031897</v>
+        <v>7031895</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
         <v>31</v>
       </c>
       <c r="H14" s="1"/>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L14">
-        <v>1711329</v>
+        <v>1706681</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N14" s="2">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="O14" s="2">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="Q14" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="R14" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="S14" t="s">
         <v>20</v>
       </c>
       <c r="T14">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="B15">
-        <v>7031897</v>
+        <v>7031895</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
         <v>31</v>
       </c>
       <c r="H15" s="1"/>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L15">
-        <v>1715169</v>
+        <v>1708464</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="N15" s="2">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="O15" s="2">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="P15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="s">
         <v>20</v>
       </c>
       <c r="R15" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="S15" t="s">
         <v>20</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>332</v>
+        <v>175</v>
       </c>
       <c r="B16">
-        <v>7031897</v>
+        <v>7031895</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
         <v>31</v>
       </c>
       <c r="H16" s="1"/>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L16">
-        <v>1723203</v>
+        <v>1715169</v>
       </c>
       <c r="M16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="N16" s="2">
-        <v>46237</v>
+        <v>46218</v>
       </c>
       <c r="O16" s="2">
-        <v>46237</v>
+        <v>46218</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="Q16" t="s">
         <v>20</v>
       </c>
       <c r="R16" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="S16" t="s">
         <v>20</v>
       </c>
       <c r="T16">
-        <v>15</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="B17">
         <v>7031897</v>
@@ -1464,7 +1482,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="B18">
         <v>7031897</v>
@@ -1515,7 +1533,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="B19">
         <v>7031897</v>
@@ -1537,36 +1555,36 @@
         <v>32</v>
       </c>
       <c r="L19">
-        <v>1706681</v>
+        <v>1710979</v>
       </c>
       <c r="M19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N19" s="2">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="O19" s="2">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="P19">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
       <c r="R19" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="S19" t="s">
         <v>20</v>
       </c>
       <c r="T19">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="B20">
         <v>7031897</v>
@@ -1588,47 +1606,185 @@
         <v>32</v>
       </c>
       <c r="L20">
-        <v>1710979</v>
+        <v>1711329</v>
       </c>
       <c r="M20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N20" s="2">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="O20" s="2">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="P20">
+        <v>90</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" t="s">
+        <v>40</v>
+      </c>
+      <c r="S20" t="s">
+        <v>20</v>
+      </c>
+      <c r="T20">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>366</v>
+      </c>
+      <c r="B21">
+        <v>7031897</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21">
+        <v>1706681</v>
+      </c>
+      <c r="M21" t="s">
+        <v>42</v>
+      </c>
+      <c r="N21" s="2">
+        <v>46218</v>
+      </c>
+      <c r="O21" s="2">
+        <v>46218</v>
+      </c>
+      <c r="P21">
+        <v>83</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" t="s">
+        <v>20</v>
+      </c>
+      <c r="T21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>367</v>
+      </c>
+      <c r="B22">
+        <v>7031897</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22">
+        <v>1723203</v>
+      </c>
+      <c r="M22" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="2">
+        <v>46237</v>
+      </c>
+      <c r="O22" s="2">
+        <v>46237</v>
+      </c>
+      <c r="P22">
         <v>100</v>
       </c>
-      <c r="Q20" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" t="s">
-        <v>41</v>
-      </c>
-      <c r="S20" t="s">
-        <v>20</v>
-      </c>
-      <c r="T20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H21" s="1"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H22" s="1"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="Q22" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" t="s">
+        <v>58</v>
+      </c>
+      <c r="S22" t="s">
+        <v>20</v>
+      </c>
+      <c r="T22">
+        <v>15</v>
+      </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>368</v>
+      </c>
+      <c r="B23">
+        <v>7031897</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
       <c r="H23" s="1"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>1715169</v>
+      </c>
+      <c r="M23" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="2">
+        <v>46217</v>
+      </c>
+      <c r="O23" s="2">
+        <v>46217</v>
+      </c>
+      <c r="P23">
+        <v>75</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" t="s">
+        <v>20</v>
+      </c>
+      <c r="T23">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H24" s="1"/>

--- a/exames.xlsx
+++ b/exames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA382575-B11E-4EAC-9EE2-CBBBE116FA0F}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C06993E1-15A0-4275-8360-C76BC6EB72CC}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="188">
   <si>
     <t/>
   </si>
@@ -88,9 +88,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Avaliação Modular  -  Escrita Fiscal I</t>
-  </si>
-  <si>
     <t>Gabriel Monteiro</t>
   </si>
   <si>
@@ -100,18 +97,12 @@
     <t>SP/Interior</t>
   </si>
   <si>
-    <t>86621237-8df6-4ef9-99c0-0e08e5370074</t>
-  </si>
-  <si>
     <t>Giacomo Urbini</t>
   </si>
   <si>
     <t>giacomo.urbini@thomsonreuters.com</t>
   </si>
   <si>
-    <t>723c274b-ab71-4453-86d8-0af283a15e2a</t>
-  </si>
-  <si>
     <t>Rodrigo Soares</t>
   </si>
   <si>
@@ -124,60 +115,6 @@
     <t>UniRio</t>
   </si>
   <si>
-    <t>209d6921-cbbc-45b5-9977-4cdf75580790</t>
-  </si>
-  <si>
-    <t>Avaliação Modular -  Contabilidade I</t>
-  </si>
-  <si>
-    <t>20bc725a-4146-405c-a126-30ec65bb0b19</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Honorários I</t>
-  </si>
-  <si>
-    <t>ae39923f-7dd4-45e4-bdee-85cfc6bf344e</t>
-  </si>
-  <si>
-    <t>bceadea9-1e04-43b7-a81e-5a80c0928832</t>
-  </si>
-  <si>
-    <t>e6383947-4f3f-4863-8763-a392a0afdc23</t>
-  </si>
-  <si>
-    <t>8ec315c1-e0b4-41e9-9e6d-c00aa723b734</t>
-  </si>
-  <si>
-    <t>4a94a277-ccc0-4f1c-be4f-80dffe4e6203</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Folha de Pagamento - I</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>cda575fa-ff2b-4ff7-bd03-10054a15a324</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Onvio/Processos e Messenger</t>
-  </si>
-  <si>
-    <t>1965b0bf-014c-475e-a88b-ec23d2cb7aee</t>
-  </si>
-  <si>
-    <t>2d3e88f0-e94f-49fc-b19b-101d27623207</t>
-  </si>
-  <si>
-    <t>1d440a09-79e6-42e4-8fc4-fb3415cd3cbd</t>
-  </si>
-  <si>
-    <t>48c3c5ab-be40-41fb-9e0c-fc1e75ddc72b</t>
-  </si>
-  <si>
-    <t>b93caca5-b4fb-4459-bb9f-da4d67daa626</t>
-  </si>
-  <si>
     <t>EDISON NEVES</t>
   </si>
   <si>
@@ -217,7 +154,439 @@
     <t>46d21eb7-dde8-4007-b693-7428cc05b0a9</t>
   </si>
   <si>
-    <t>2f8f76a1-e71d-43b2-ab6f-835104bf2b1b</t>
+    <t>ALEXANDRE MADUREIRA MACIEL BIANCO</t>
+  </si>
+  <si>
+    <t>alexandre.madureiramacielbianco@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>6c45df13-ff47-40e9-b007-6ca856141dff</t>
+  </si>
+  <si>
+    <t>Executivo de Vendas - IV</t>
+  </si>
+  <si>
+    <t>ATILA DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>atila.demedeiros@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>Executivo Vendas - III</t>
+  </si>
+  <si>
+    <t>ad893059-3a4c-4d1c-87a4-0c70162970d9</t>
+  </si>
+  <si>
+    <t>Adriano Dos Santos</t>
+  </si>
+  <si>
+    <t>adriano.dossantos@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>5ce88d6d-afd5-4544-be0a-e7f0831a7666</t>
+  </si>
+  <si>
+    <t>Ana Beatriz</t>
+  </si>
+  <si>
+    <t>anabeatriz.vaqueiro@toolbusiness.com.br</t>
+  </si>
+  <si>
+    <t>fa354307-4fde-4bf5-9593-e23930ae8e28</t>
+  </si>
+  <si>
+    <t>a5a2a4dc-5519-46c5-a1a8-92e72d8c178b</t>
+  </si>
+  <si>
+    <t>9018332f-a92a-43a1-9c6b-dec34471b8ff</t>
+  </si>
+  <si>
+    <t>BRUNA MOREIRA</t>
+  </si>
+  <si>
+    <t>bruna.moreira@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>eeb70dfd-c213-450c-9f9c-efa8cd20a5cd</t>
+  </si>
+  <si>
+    <t>Barbara Duarte</t>
+  </si>
+  <si>
+    <t>barbara.duarte@dominiochapeco.com.br</t>
+  </si>
+  <si>
+    <t>d587564f-18c6-4322-a5cf-725191ac459a</t>
+  </si>
+  <si>
+    <t>Bispo</t>
+  </si>
+  <si>
+    <t>talles.bispo@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>0e425368-a329-4a57-9ba1-5ccad78711f8</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>bruno.melo@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>5e912ab8-61e0-470a-b1f2-360ca2b51f94</t>
+  </si>
+  <si>
+    <t>CAMILA TAVARES</t>
+  </si>
+  <si>
+    <t>camila.tavares@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>5785ad96-2f9a-457c-a65e-8f6de6555124</t>
+  </si>
+  <si>
+    <t>CARLA DAS CHAGAS ROSA DELOMO</t>
+  </si>
+  <si>
+    <t>carla.daschagasrosadelomo@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>b53a70af-33b0-4ca2-96ff-9a3cdc3f373e</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>carlos.caterino@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>b5069c5c-9f2a-465e-8f4b-26e6faebfe27</t>
+  </si>
+  <si>
+    <t>Claudenir Lourenco Santos</t>
+  </si>
+  <si>
+    <t>claudenirlourenco.santos@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>1cddf3f1-eb78-4532-a7a8-f803228c99c7</t>
+  </si>
+  <si>
+    <t>Cristiane Pereira dos Santos</t>
+  </si>
+  <si>
+    <t>cristiane.pereiradossantos@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>e4da6ed6-493e-41ee-ac78-329533aca15a</t>
+  </si>
+  <si>
+    <t>DANIEL JORGE NETO</t>
+  </si>
+  <si>
+    <t>daniel.jorge@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>aa2bf327-f02c-4ee3-ad7f-52fb52651d3c</t>
+  </si>
+  <si>
+    <t>DANIELA MENDES CARDOSO</t>
+  </si>
+  <si>
+    <t>daniela.mendescardoso@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>a68def65-2c5a-4e0f-9dcd-4410ad9d684c</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>diego.hora@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>f2722ff2-f050-4e6c-9b6e-da5c26a5885b</t>
+  </si>
+  <si>
+    <t>Executivo de Vendas - V</t>
+  </si>
+  <si>
+    <t>Emelein Kretschmer da Rosa</t>
+  </si>
+  <si>
+    <t>emelein.kretschmer@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>Executivo de Venda - III</t>
+  </si>
+  <si>
+    <t>d63b4e63-7cfe-4ae9-8ffb-fe2d00d03fe2</t>
+  </si>
+  <si>
+    <t>FELIPE MAZIERO</t>
+  </si>
+  <si>
+    <t>felipe.maziero@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>b470b322-8aeb-4b2b-9053-6641c114a67d</t>
+  </si>
+  <si>
+    <t>GABRIEL DA SILVA MACHADO</t>
+  </si>
+  <si>
+    <t>g.machado@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>35869e2e-4c78-464e-933e-93f16ef71a07</t>
+  </si>
+  <si>
+    <t>GABRIELA DE OLIVEIRA PINHEIRO</t>
+  </si>
+  <si>
+    <t>gabriela.pinheiro@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>922d172d-7a58-46b3-8304-87597a751855</t>
+  </si>
+  <si>
+    <t>GUILHERME JANUÁRIO</t>
+  </si>
+  <si>
+    <t>guilherme.januario@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>584df6d8-fdcd-4255-9b34-306e3cae1f84</t>
+  </si>
+  <si>
+    <t>Executivo de Vendas II</t>
+  </si>
+  <si>
+    <t>Executivo de Vendas - II</t>
+  </si>
+  <si>
+    <t>Guilherme Oliveira de Carvalho Lopes</t>
+  </si>
+  <si>
+    <t>guilherme.oliveiracarvalholopes@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>141e8126-a4ad-4367-8ab2-49b3f8a27046</t>
+  </si>
+  <si>
+    <t>IGOR AMARAL</t>
+  </si>
+  <si>
+    <t>igor.amaral@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>e3072fff-253b-401e-9b2e-5a8501f5de1c</t>
+  </si>
+  <si>
+    <t>ISABELA CRUZ</t>
+  </si>
+  <si>
+    <t>isabele.cruz@2bst.com.br</t>
+  </si>
+  <si>
+    <t>c1525787-b169-43bd-b1d5-9170b96f6b55</t>
+  </si>
+  <si>
+    <t>Igor.Ascard@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>igor.ascard@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>c0e23b75-5616-45ac-aa4f-4889dba939f5</t>
+  </si>
+  <si>
+    <t>Isabelle</t>
+  </si>
+  <si>
+    <t>isabelle.delima@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>0ddf4114-b40c-47bd-a82d-1d278306f250</t>
+  </si>
+  <si>
+    <t>JEAN CARLOS BRITO DE ARAÚJO</t>
+  </si>
+  <si>
+    <t>jeancarlos.araujo@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>536f99dc-0b76-491e-be2f-95dc82b56a0d</t>
+  </si>
+  <si>
+    <t>JOSE VINICIUS GENARO</t>
+  </si>
+  <si>
+    <t>josevinicius.genaro@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>ADRIANE INÊS BUZANELLO</t>
+  </si>
+  <si>
+    <t>b86aab68-c509-49ec-a014-30a27d7505fe</t>
+  </si>
+  <si>
+    <t>LARISSA DA ROCHA ROSSO</t>
+  </si>
+  <si>
+    <t>larissa.rosso@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>f70c6295-cc5b-4c06-8c1f-cb1d2268c73c</t>
+  </si>
+  <si>
+    <t>a1609bd8-bfb4-414d-a764-2775cf482f62</t>
+  </si>
+  <si>
+    <t>b9f81943-9058-499c-887e-f4c206198684</t>
+  </si>
+  <si>
+    <t>LEON PEREIRA FERREIRA</t>
+  </si>
+  <si>
+    <t>leon.pereiraferreira@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>4fe49c3c-3cf9-437f-8d31-6d90e225d926</t>
+  </si>
+  <si>
+    <t>LUCILÂNDIA SOCORRO DE SÁ</t>
+  </si>
+  <si>
+    <t>lucy.sa@2bst.com.br</t>
+  </si>
+  <si>
+    <t>26d38554-b8af-4fe6-9c2c-7e9bad5db9a6</t>
+  </si>
+  <si>
+    <t>Luis Henrique Guedes</t>
+  </si>
+  <si>
+    <t>luishenrique.guedes@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>a0e84e12-ad1b-4a5a-9ebe-bf2f675dfc46</t>
+  </si>
+  <si>
+    <t>MARCELO JANUARIO</t>
+  </si>
+  <si>
+    <t>marcelo.januario@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>6850ac06-1356-40d4-8a3e-aa6e5e945202</t>
+  </si>
+  <si>
+    <t>MARCO LANZER</t>
+  </si>
+  <si>
+    <t>marco.lanzer@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>2cc77553-4e99-41c5-96c8-6669f72b32e6</t>
+  </si>
+  <si>
+    <t>Marcelo Didolich</t>
+  </si>
+  <si>
+    <t>marcelo.didolich@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>ed83d610-81d2-44b4-8d8b-944a858e6873</t>
+  </si>
+  <si>
+    <t>Natalia</t>
+  </si>
+  <si>
+    <t>natalia.costa@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>d2f491d7-a145-4c62-a479-036055caaaba</t>
+  </si>
+  <si>
+    <t>RODRIGO DA CUNHA</t>
+  </si>
+  <si>
+    <t>rodrigo.dacunha@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>cf4ba90c-630a-427c-8a79-934355562f79</t>
+  </si>
+  <si>
+    <t>RODRIGO SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>rodrigo.santosdasilva@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>2dea7d3d-582c-40d1-b8c4-45502c4ee2e9</t>
+  </si>
+  <si>
+    <t>STELA DA SILVA</t>
+  </si>
+  <si>
+    <t>stela.dasilva@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>00357a4a-7f7b-42eb-a031-6d5f98684529</t>
+  </si>
+  <si>
+    <t>THAIS DANTAS</t>
+  </si>
+  <si>
+    <t>thais.dantas@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>93a6eaf8-8215-491a-992f-18ba398bfe18</t>
+  </si>
+  <si>
+    <t>Victor Widmann</t>
+  </si>
+  <si>
+    <t>victorhugo.widmann@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>95fb9702-eb81-4530-8195-b22abf34d64c</t>
+  </si>
+  <si>
+    <t>Vinicius Miranda</t>
+  </si>
+  <si>
+    <t>vinicius.miranda@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>f39d7290-9411-465f-aa3b-696c20699d51</t>
+  </si>
+  <si>
+    <t>Wallace Matos</t>
+  </si>
+  <si>
+    <t>wallace.matos@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>1c749d7a-4def-4cbd-8f85-dd657740ea50</t>
+  </si>
+  <si>
+    <t>5eda88d2-3206-4fcf-bbf0-b6d9e5404a83</t>
+  </si>
+  <si>
+    <t>flavia.ferreira@2bst.com.br</t>
+  </si>
+  <si>
+    <t>3cec2a94-2230-41b0-802b-44013292b390</t>
+  </si>
+  <si>
+    <t>willian.duarte@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>262ce6c3-bd31-44b3-8411-a6a03a493bea</t>
   </si>
 </sst>
 </file>
@@ -257,7 +626,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -665,1328 +1037,2809 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="3">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3368455</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O2" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P2" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>42</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="3">
         <v>3394166</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P3" s="3">
+        <v>80</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3779500</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P4" s="3">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3">
+        <v>6429180</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O5" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P5" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T5" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6033759</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="5">
+        <v>46244</v>
+      </c>
+      <c r="O6" s="5">
+        <v>46244</v>
+      </c>
+      <c r="P6" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3">
+        <v>6033759</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="5">
+        <v>46244</v>
+      </c>
+      <c r="O7" s="5">
+        <v>46244</v>
+      </c>
+      <c r="P7" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>67</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6033759</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="5">
+        <v>46244</v>
+      </c>
+      <c r="O8" s="5">
+        <v>46244</v>
+      </c>
+      <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>85</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3368423</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="5">
+        <v>46239</v>
+      </c>
+      <c r="O9" s="5">
+        <v>46239</v>
+      </c>
+      <c r="P9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T9" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>86</v>
+      </c>
+      <c r="B10" s="3">
+        <v>6192692</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O10" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T10" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>87</v>
+      </c>
+      <c r="B11" s="3">
+        <v>6159220</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="5">
+        <v>46240</v>
+      </c>
+      <c r="O11" s="5">
+        <v>46240</v>
+      </c>
+      <c r="P11" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T11" s="3">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>88</v>
+      </c>
+      <c r="B12" s="3">
+        <v>6222316</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" s="5">
+        <v>46244</v>
+      </c>
+      <c r="O12" s="5">
+        <v>46244</v>
+      </c>
+      <c r="P12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T12" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>90</v>
+      </c>
+      <c r="B13" s="3">
+        <v>3391206</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O13" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P13" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T13" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>91</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3797742</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O14" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T14" s="3">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>102</v>
+      </c>
+      <c r="B15" s="3">
+        <v>6091089</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="5">
+        <v>46240</v>
+      </c>
+      <c r="O15" s="5">
+        <v>46240</v>
+      </c>
+      <c r="P15" s="3">
+        <v>70</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T15" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>107</v>
+      </c>
+      <c r="B16" s="3">
+        <v>6433541</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O16" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P16" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T16" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>108</v>
+      </c>
+      <c r="B17" s="3">
+        <v>6386086</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="5">
+        <v>46240</v>
+      </c>
+      <c r="O17" s="5">
+        <v>46240</v>
+      </c>
+      <c r="P17" s="3">
+        <v>80</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T17" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>114</v>
+      </c>
+      <c r="B18" s="3">
+        <v>3371119</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O18" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T18" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>115</v>
+      </c>
+      <c r="B19" s="3">
+        <v>3369232</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N19" s="5">
+        <v>46244</v>
+      </c>
+      <c r="O19" s="5">
+        <v>46244</v>
+      </c>
+      <c r="P19" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T19" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3">
+        <v>6232612</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O20" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T20" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>126</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3377344</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2">
+      <c r="E21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O21" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P21" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T21" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>144</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4543344</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3">
         <v>1724178</v>
       </c>
-      <c r="M2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" s="2">
+      <c r="M22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N22" s="5">
         <v>46241</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O22" s="5">
         <v>46241</v>
       </c>
-      <c r="P2">
+      <c r="P22" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T22" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>152</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3377347</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N23" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O23" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T23" s="3">
+        <v>5242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>159</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3377007</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O24" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T24" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>160</v>
+      </c>
+      <c r="B25" s="3">
+        <v>3367693</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N25" s="5">
+        <v>46239</v>
+      </c>
+      <c r="O25" s="5">
+        <v>46239</v>
+      </c>
+      <c r="P25" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T25" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>162</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3371022</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N26" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O26" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P26" s="3">
         <v>80</v>
       </c>
-      <c r="Q2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" t="s">
-        <v>62</v>
-      </c>
-      <c r="S2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T2">
+      <c r="Q26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T26" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>166</v>
+      </c>
+      <c r="B27" s="3">
+        <v>7031896</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N27" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O27" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P27" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>175</v>
+      </c>
+      <c r="B28" s="3">
+        <v>7031895</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O28" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P28" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T28" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>184</v>
+      </c>
+      <c r="B29" s="3">
+        <v>6345154</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N29" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O29" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P29" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T29" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3">
+        <v>3370070</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N30" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O30" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P30" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T30" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>187</v>
+      </c>
+      <c r="B31" s="3">
+        <v>3367914</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N31" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O31" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P31" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T31" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>189</v>
+      </c>
+      <c r="B32" s="3">
+        <v>4745431</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N32" s="5">
+        <v>46239</v>
+      </c>
+      <c r="O32" s="5">
+        <v>46239</v>
+      </c>
+      <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T32" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>192</v>
+      </c>
+      <c r="B33" s="3">
+        <v>6222314</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" s="5">
+        <v>46240</v>
+      </c>
+      <c r="O33" s="5">
+        <v>46240</v>
+      </c>
+      <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T33" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>193</v>
+      </c>
+      <c r="B34" s="3">
+        <v>3394648</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N34" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O34" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P34" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T34" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>195</v>
+      </c>
+      <c r="B35" s="3">
+        <v>3797743</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O35" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T35" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>225</v>
+      </c>
+      <c r="B36" s="3">
+        <v>3406205</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N36" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O36" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P36" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T36" s="3">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>226</v>
+      </c>
+      <c r="B37" s="3">
+        <v>3406205</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O37" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P37" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T37" s="3">
+        <v>7259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>227</v>
+      </c>
+      <c r="B38" s="3">
+        <v>3406205</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N38" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O38" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P38" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T38" s="3">
+        <v>7271</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>228</v>
+      </c>
+      <c r="B39" s="3">
+        <v>3379507</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O39" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P39" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T39" s="3">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>237</v>
+      </c>
+      <c r="B40" s="3">
+        <v>3369242</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N40" s="5">
+        <v>46243</v>
+      </c>
+      <c r="O40" s="5">
+        <v>46243</v>
+      </c>
+      <c r="P40" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T40" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>284</v>
+      </c>
+      <c r="B41" s="3">
+        <v>6921313</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N41" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O41" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P41" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T41" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>285</v>
+      </c>
+      <c r="B42" s="3">
+        <v>3377339</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O42" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P42" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T42" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>295</v>
+      </c>
+      <c r="B43" s="3">
+        <v>3377346</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N43" s="5">
+        <v>46244</v>
+      </c>
+      <c r="O43" s="5">
+        <v>46244</v>
+      </c>
+      <c r="P43" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T43" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>320</v>
+      </c>
+      <c r="B44" s="3">
+        <v>4745432</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N44" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O44" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P44" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T44" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>327</v>
+      </c>
+      <c r="B45" s="3">
+        <v>6232613</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N45" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O45" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T45" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>356</v>
+      </c>
+      <c r="B46" s="3">
+        <v>3371025</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N46" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O46" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T46" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>357</v>
+      </c>
+      <c r="B47" s="3">
+        <v>3367776</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N47" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O47" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P47" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T47" s="3">
+        <v>5498</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>368</v>
+      </c>
+      <c r="B48" s="3">
+        <v>7031897</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N48" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O48" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T48" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>369</v>
+      </c>
+      <c r="B49" s="3">
+        <v>3371114</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N49" s="5">
+        <v>46241</v>
+      </c>
+      <c r="O49" s="5">
+        <v>46241</v>
+      </c>
+      <c r="P49" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>126</v>
-      </c>
-      <c r="B3">
-        <v>3377344</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="J3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3">
+      <c r="Q49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T49" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>372</v>
+      </c>
+      <c r="B50" s="3">
+        <v>3372145</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N50" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O50" s="5">
+        <v>46237</v>
+      </c>
+      <c r="P50" s="3">
+        <v>90</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T50" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>393</v>
+      </c>
+      <c r="B51" s="3">
+        <v>5005208</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3">
         <v>1724163</v>
       </c>
-      <c r="M3" t="s">
-        <v>54</v>
-      </c>
-      <c r="N3" s="2">
+      <c r="M51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N51" s="5">
+        <v>46239</v>
+      </c>
+      <c r="O51" s="5">
+        <v>46239</v>
+      </c>
+      <c r="P51" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T51" s="3">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>396</v>
+      </c>
+      <c r="B52" s="3">
+        <v>6484813</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N52" s="5">
+        <v>46238</v>
+      </c>
+      <c r="O52" s="5">
+        <v>46238</v>
+      </c>
+      <c r="P52" s="3">
+        <v>80</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T52" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>404</v>
+      </c>
+      <c r="B53" s="3">
+        <v>5816942</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3">
+        <v>1723203</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N53" s="5">
+        <v>46232</v>
+      </c>
+      <c r="O53" s="5">
+        <v>46232</v>
+      </c>
+      <c r="P53" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T53" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>406</v>
+      </c>
+      <c r="B54" s="3">
+        <v>5816942</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N54" s="5">
+        <v>46232</v>
+      </c>
+      <c r="O54" s="5">
+        <v>46232</v>
+      </c>
+      <c r="P54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T54" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>419</v>
+      </c>
+      <c r="B55" s="3">
+        <v>4264886</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3">
+        <v>1724163</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N55" s="5">
+        <v>46240</v>
+      </c>
+      <c r="O55" s="5">
+        <v>46240</v>
+      </c>
+      <c r="P55" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T55" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>429</v>
+      </c>
+      <c r="B56" s="3">
+        <v>5360489</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3">
+        <v>1724178</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N56" s="5">
         <v>46237</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O56" s="5">
         <v>46237</v>
       </c>
-      <c r="P3">
-        <v>90</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S3" t="s">
-        <v>20</v>
-      </c>
-      <c r="T3">
+      <c r="P56" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T56" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>163</v>
-      </c>
-      <c r="B4">
-        <v>7031896</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>1711329</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2">
-        <v>46213</v>
-      </c>
-      <c r="O4" s="2">
-        <v>46213</v>
-      </c>
-      <c r="P4">
-        <v>90</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>20</v>
-      </c>
-      <c r="R4" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" t="s">
-        <v>20</v>
-      </c>
-      <c r="T4">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>164</v>
-      </c>
-      <c r="B5">
-        <v>7031896</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
-        <v>1706681</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="2">
-        <v>46218</v>
-      </c>
-      <c r="O5" s="2">
-        <v>46218</v>
-      </c>
-      <c r="P5">
-        <v>83</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" t="s">
-        <v>20</v>
-      </c>
-      <c r="T5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>165</v>
-      </c>
-      <c r="B6">
-        <v>7031896</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>1715169</v>
-      </c>
-      <c r="M6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="2">
-        <v>46217</v>
-      </c>
-      <c r="O6" s="2">
-        <v>46217</v>
-      </c>
-      <c r="P6">
-        <v>83</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S6" t="s">
-        <v>20</v>
-      </c>
-      <c r="T6">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>166</v>
-      </c>
-      <c r="B7">
-        <v>7031896</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7">
-        <v>1724163</v>
-      </c>
-      <c r="M7" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="2">
-        <v>46238</v>
-      </c>
-      <c r="O7" s="2">
-        <v>46238</v>
-      </c>
-      <c r="P7">
-        <v>90</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S7" t="s">
-        <v>20</v>
-      </c>
-      <c r="T7">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>167</v>
-      </c>
-      <c r="B8">
-        <v>7031896</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>1708464</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="2">
-        <v>46211</v>
-      </c>
-      <c r="O8" s="2">
-        <v>46211</v>
-      </c>
-      <c r="P8">
-        <v>80</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>20</v>
-      </c>
-      <c r="R8" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8" t="s">
-        <v>20</v>
-      </c>
-      <c r="T8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>168</v>
-      </c>
-      <c r="B9">
-        <v>7031896</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9">
-        <v>1710979</v>
-      </c>
-      <c r="M9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N9" s="2">
-        <v>46216</v>
-      </c>
-      <c r="O9" s="2">
-        <v>46216</v>
-      </c>
-      <c r="P9">
-        <v>100</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>20</v>
-      </c>
-      <c r="R9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>169</v>
-      </c>
-      <c r="B10">
-        <v>7031895</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="J10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10">
-        <v>1724163</v>
-      </c>
-      <c r="M10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" s="2">
-        <v>46238</v>
-      </c>
-      <c r="O10" s="2">
-        <v>46238</v>
-      </c>
-      <c r="P10">
-        <v>90</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>20</v>
-      </c>
-      <c r="R10" t="s">
-        <v>63</v>
-      </c>
-      <c r="S10" t="s">
-        <v>20</v>
-      </c>
-      <c r="T10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>170</v>
-      </c>
-      <c r="B11">
-        <v>7031895</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11">
-        <v>1710979</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="2">
-        <v>46216</v>
-      </c>
-      <c r="O11" s="2">
-        <v>46216</v>
-      </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11" t="s">
-        <v>39</v>
-      </c>
-      <c r="S11" t="s">
-        <v>20</v>
-      </c>
-      <c r="T11">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>171</v>
-      </c>
-      <c r="B12">
-        <v>7031895</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12">
-        <v>1706681</v>
-      </c>
-      <c r="M12" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12" s="2">
-        <v>46238</v>
-      </c>
-      <c r="O12" s="2">
-        <v>46238</v>
-      </c>
-      <c r="P12">
-        <v>83</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>20</v>
-      </c>
-      <c r="R12" t="s">
-        <v>64</v>
-      </c>
-      <c r="S12" t="s">
-        <v>20</v>
-      </c>
-      <c r="T12">
-        <v>28480</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>172</v>
-      </c>
-      <c r="B13">
-        <v>7031895</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13">
-        <v>1711329</v>
-      </c>
-      <c r="M13" t="s">
-        <v>34</v>
-      </c>
-      <c r="N13" s="2">
-        <v>46213</v>
-      </c>
-      <c r="O13" s="2">
-        <v>46213</v>
-      </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>20</v>
-      </c>
-      <c r="R13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S13" t="s">
-        <v>20</v>
-      </c>
-      <c r="T13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>173</v>
-      </c>
-      <c r="B14">
-        <v>7031895</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14">
-        <v>1706681</v>
-      </c>
-      <c r="M14" t="s">
-        <v>42</v>
-      </c>
-      <c r="N14" s="2">
-        <v>46218</v>
-      </c>
-      <c r="O14" s="2">
-        <v>46218</v>
-      </c>
-      <c r="P14">
-        <v>67</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>43</v>
-      </c>
-      <c r="R14" t="s">
-        <v>48</v>
-      </c>
-      <c r="S14" t="s">
-        <v>20</v>
-      </c>
-      <c r="T14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>174</v>
-      </c>
-      <c r="B15">
-        <v>7031895</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="J15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15">
-        <v>1708464</v>
-      </c>
-      <c r="M15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="2">
-        <v>46211</v>
-      </c>
-      <c r="O15" s="2">
-        <v>46211</v>
-      </c>
-      <c r="P15">
-        <v>50</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15" t="s">
-        <v>28</v>
-      </c>
-      <c r="S15" t="s">
-        <v>20</v>
-      </c>
-      <c r="T15">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>175</v>
-      </c>
-      <c r="B16">
-        <v>7031895</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="J16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16">
-        <v>1715169</v>
-      </c>
-      <c r="M16" t="s">
-        <v>45</v>
-      </c>
-      <c r="N16" s="2">
-        <v>46218</v>
-      </c>
-      <c r="O16" s="2">
-        <v>46218</v>
-      </c>
-      <c r="P16">
-        <v>83</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>20</v>
-      </c>
-      <c r="R16" t="s">
-        <v>47</v>
-      </c>
-      <c r="S16" t="s">
-        <v>20</v>
-      </c>
-      <c r="T16">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>362</v>
-      </c>
-      <c r="B17">
-        <v>7031897</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="J17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17">
-        <v>1715169</v>
-      </c>
-      <c r="M17" t="s">
-        <v>45</v>
-      </c>
-      <c r="N17" s="2">
-        <v>46217</v>
-      </c>
-      <c r="O17" s="2">
-        <v>46217</v>
-      </c>
-      <c r="P17">
-        <v>50</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>43</v>
-      </c>
-      <c r="R17" t="s">
-        <v>49</v>
-      </c>
-      <c r="S17" t="s">
-        <v>43</v>
-      </c>
-      <c r="T17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>363</v>
-      </c>
-      <c r="B18">
-        <v>7031897</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18">
-        <v>1708464</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="2">
-        <v>46211</v>
-      </c>
-      <c r="O18" s="2">
-        <v>46211</v>
-      </c>
-      <c r="P18">
-        <v>70</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>20</v>
-      </c>
-      <c r="R18" t="s">
-        <v>33</v>
-      </c>
-      <c r="S18" t="s">
-        <v>20</v>
-      </c>
-      <c r="T18">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>364</v>
-      </c>
-      <c r="B19">
-        <v>7031897</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19">
-        <v>1710979</v>
-      </c>
-      <c r="M19" t="s">
-        <v>36</v>
-      </c>
-      <c r="N19" s="2">
-        <v>46216</v>
-      </c>
-      <c r="O19" s="2">
-        <v>46216</v>
-      </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>20</v>
-      </c>
-      <c r="R19" t="s">
-        <v>41</v>
-      </c>
-      <c r="S19" t="s">
-        <v>20</v>
-      </c>
-      <c r="T19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>365</v>
-      </c>
-      <c r="B20">
-        <v>7031897</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20">
-        <v>1711329</v>
-      </c>
-      <c r="M20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N20" s="2">
-        <v>46213</v>
-      </c>
-      <c r="O20" s="2">
-        <v>46213</v>
-      </c>
-      <c r="P20">
-        <v>90</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" t="s">
-        <v>40</v>
-      </c>
-      <c r="S20" t="s">
-        <v>20</v>
-      </c>
-      <c r="T20">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>366</v>
-      </c>
-      <c r="B21">
-        <v>7031897</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="J21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21">
-        <v>1706681</v>
-      </c>
-      <c r="M21" t="s">
-        <v>42</v>
-      </c>
-      <c r="N21" s="2">
-        <v>46218</v>
-      </c>
-      <c r="O21" s="2">
-        <v>46218</v>
-      </c>
-      <c r="P21">
-        <v>83</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21" t="s">
-        <v>50</v>
-      </c>
-      <c r="S21" t="s">
-        <v>20</v>
-      </c>
-      <c r="T21">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>367</v>
-      </c>
-      <c r="B22">
-        <v>7031897</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="J22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22">
-        <v>1723203</v>
-      </c>
-      <c r="M22" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="2">
-        <v>46237</v>
-      </c>
-      <c r="O22" s="2">
-        <v>46237</v>
-      </c>
-      <c r="P22">
-        <v>100</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>20</v>
-      </c>
-      <c r="R22" t="s">
-        <v>58</v>
-      </c>
-      <c r="S22" t="s">
-        <v>20</v>
-      </c>
-      <c r="T22">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>368</v>
-      </c>
-      <c r="B23">
-        <v>7031897</v>
-      </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="J23" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23">
-        <v>1715169</v>
-      </c>
-      <c r="M23" t="s">
-        <v>45</v>
-      </c>
-      <c r="N23" s="2">
-        <v>46217</v>
-      </c>
-      <c r="O23" s="2">
-        <v>46217</v>
-      </c>
-      <c r="P23">
-        <v>75</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>20</v>
-      </c>
-      <c r="R23" t="s">
-        <v>49</v>
-      </c>
-      <c r="S23" t="s">
-        <v>20</v>
-      </c>
-      <c r="T23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H24" s="1"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H25" s="1"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H26" s="1"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H27" s="1"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H28" s="1"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H29" s="1"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H30" s="1"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H31" s="1"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H32" s="1"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H33" s="1"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H34" s="1"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H35" s="1"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H36" s="1"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H37" s="1"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H38" s="1"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H39" s="1"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H40" s="1"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-    </row>
-    <row r="41" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H41" s="1"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-    </row>
-    <row r="42" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H42" s="1"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-    </row>
-    <row r="43" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H43" s="1"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-    </row>
-    <row r="44" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H44" s="1"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-    </row>
-    <row r="45" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H45" s="1"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-    </row>
-    <row r="46" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H46" s="1"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-    </row>
-    <row r="47" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H47" s="1"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-    </row>
-    <row r="48" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H48" s="1"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-    </row>
-    <row r="49" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H49" s="1"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-    </row>
-    <row r="50" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H50" s="1"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-    </row>
-    <row r="51" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H51" s="1"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-    </row>
-    <row r="52" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H52" s="1"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-    </row>
-    <row r="53" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H53" s="1"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-    </row>
-    <row r="54" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H54" s="1"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-    </row>
-    <row r="55" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H55" s="1"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-    </row>
-    <row r="56" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H56" s="1"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-    </row>
-    <row r="57" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H57" s="1"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H58" s="1"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H59" s="1"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H60" s="1"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H61" s="1"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H62" s="1"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H63" s="1"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H64" s="1"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>

--- a/exames.xlsx
+++ b/exames.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trten-my.sharepoint.com/personal/lucas_machado_thomsonreuters_com/Documents/Desktop/Ven/tr-intelligence - testes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9CDCCF5-785C-4639-8B49-4E94EB9E59CC}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_F340A05831385EDFDA183BB921514E23317A6EF1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C494DDB8-6273-4FED-9014-6AF21F137075}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-2220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$T$345</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="336">
   <si>
     <t/>
   </si>
@@ -529,66 +529,6 @@
     <t>2dea7d3d-582c-40d1-b8c4-45502c4ee2e9</t>
   </si>
   <si>
-    <t>STELA DA SILVA</t>
-  </si>
-  <si>
-    <t>stela.dasilva@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>00357a4a-7f7b-42eb-a031-6d5f98684529</t>
-  </si>
-  <si>
-    <t>THAIS DANTAS</t>
-  </si>
-  <si>
-    <t>thais.dantas@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>93a6eaf8-8215-491a-992f-18ba398bfe18</t>
-  </si>
-  <si>
-    <t>Victor Widmann</t>
-  </si>
-  <si>
-    <t>victorhugo.widmann@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>95fb9702-eb81-4530-8195-b22abf34d64c</t>
-  </si>
-  <si>
-    <t>Vinicius Miranda</t>
-  </si>
-  <si>
-    <t>vinicius.miranda@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>f39d7290-9411-465f-aa3b-696c20699d51</t>
-  </si>
-  <si>
-    <t>Wallace Matos</t>
-  </si>
-  <si>
-    <t>wallace.matos@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>1c749d7a-4def-4cbd-8f85-dd657740ea50</t>
-  </si>
-  <si>
-    <t>5eda88d2-3206-4fcf-bbf0-b6d9e5404a83</t>
-  </si>
-  <si>
-    <t>flavia.ferreira@2bst.com.br</t>
-  </si>
-  <si>
-    <t>3cec2a94-2230-41b0-802b-44013292b390</t>
-  </si>
-  <si>
-    <t>willian.duarte@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>262ce6c3-bd31-44b3-8411-a6a03a493bea</t>
-  </si>
-  <si>
     <t>Anderson Francisco da Silva Santos</t>
   </si>
   <si>
@@ -619,6 +559,30 @@
     <t>c8fec5d8-d774-4ca5-b4f1-3ba3b8c08f64</t>
   </si>
   <si>
+    <t>BRUNO LOLLI CIANCI</t>
+  </si>
+  <si>
+    <t>bruno@resultasolucoes.com.br</t>
+  </si>
+  <si>
+    <t>ac22cb5b-c11b-4bf4-b920-543f515e6bcc</t>
+  </si>
+  <si>
+    <t>f0d70fe3-59d9-493c-804d-d3cd56e7f8e9</t>
+  </si>
+  <si>
+    <t>dcf7f872-5d03-438d-8616-a0a8bca1a6cc</t>
+  </si>
+  <si>
+    <t>Benhur Zuppa</t>
+  </si>
+  <si>
+    <t>benhur.zuppa@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>39148bef-67a0-4876-b041-2a71f888e004</t>
+  </si>
+  <si>
     <t>Bruna</t>
   </si>
   <si>
@@ -628,6 +592,93 @@
     <t>4e7b766a-0590-4cc6-ad2c-73e5959ff9ee</t>
   </si>
   <si>
+    <t>CLAUDIA ANDRADE</t>
+  </si>
+  <si>
+    <t>claudia.librecontabil@gmail.com</t>
+  </si>
+  <si>
+    <t>5e9dd926-c0b7-490c-850a-587b09ab6026</t>
+  </si>
+  <si>
+    <t>CONTAL CONTABILIDADE E ADMINISTRAÇÃO</t>
+  </si>
+  <si>
+    <t>contal@contal.srv.br</t>
+  </si>
+  <si>
+    <t>Avaliação Modular  -  Escrita Fiscal I</t>
+  </si>
+  <si>
+    <t>4a235493-c132-43aa-8998-06b794d9943c</t>
+  </si>
+  <si>
+    <t>Carla Pastorini</t>
+  </si>
+  <si>
+    <t>carla.pastorini@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>7df4580d-ac6c-4eac-a5d1-037de4db5b67</t>
+  </si>
+  <si>
+    <t>76048a50-233f-41ef-9071-78937d1a67ba</t>
+  </si>
+  <si>
+    <t>Avaliação Modular - Honorários I</t>
+  </si>
+  <si>
+    <t>44e38000-2ebe-4642-bc15-614a0d482f09</t>
+  </si>
+  <si>
+    <t>Avaliação Modular -  Contabilidade I</t>
+  </si>
+  <si>
+    <t>0206c101-8f04-4f29-8836-c575e7527d82</t>
+  </si>
+  <si>
+    <t>Carlos Garcia 4</t>
+  </si>
+  <si>
+    <t>carlos.garcia4@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>020dc0fe-dc06-4448-8dce-d05e2cfa5e06</t>
+  </si>
+  <si>
+    <t>Carolini Zavarise</t>
+  </si>
+  <si>
+    <t>carollini.zavarise@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>c26988e3-7ea4-47e1-8fb4-ca3744681831</t>
+  </si>
+  <si>
+    <t>5e5b7a36-a571-4f99-9daf-c780c75ddee7</t>
+  </si>
+  <si>
+    <t>261cedf7-1ffd-4712-a28b-c9d991e8b873</t>
+  </si>
+  <si>
+    <t>0e05e5ee-1876-4a7b-890c-a217061d9587</t>
+  </si>
+  <si>
+    <t>05cd5713-a85e-47cc-abdb-793e3237ef01</t>
+  </si>
+  <si>
+    <t>Cristiane Poppi</t>
+  </si>
+  <si>
+    <t>cristiane.poppi@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>942b81be-69e1-4081-bf64-a6d0ec8683e5</t>
+  </si>
+  <si>
     <t>DE MARTINI, TIAGO</t>
   </si>
   <si>
@@ -643,15 +694,12 @@
     <t>dennis.correia@thomsonreuters.com</t>
   </si>
   <si>
-    <t>Avaliação Modular  -  Escrita Fiscal I</t>
+    <t>3f4d05d7-0c76-4341-9311-0820495f157d</t>
   </si>
   <si>
     <t>c8727799-72f8-44e4-a593-0f11833dc329</t>
   </si>
   <si>
-    <t>3f4d05d7-0c76-4341-9311-0820495f157d</t>
-  </si>
-  <si>
     <t>Daniela Machado</t>
   </si>
   <si>
@@ -661,6 +709,15 @@
     <t>3d0ddc89-26d7-4a22-91d2-f21063fb63f3</t>
   </si>
   <si>
+    <t>Daniele Auler</t>
+  </si>
+  <si>
+    <t>daniele.alves@tekplan.com.br</t>
+  </si>
+  <si>
+    <t>7065cb66-c83e-4510-a82d-4e33fd580bff</t>
+  </si>
+  <si>
     <t>Derek Pazo</t>
   </si>
   <si>
@@ -676,57 +733,105 @@
     <t>elizia.brites@thomsonreuters.com</t>
   </si>
   <si>
+    <t>481d5c9a-fa16-48b0-92ea-db8521764328</t>
+  </si>
+  <si>
+    <t>04212ea5-bf2c-4cd3-9ce3-1c54a1459b91</t>
+  </si>
+  <si>
     <t>cf2ec4a7-8418-49a2-aa80-8556b365046a</t>
   </si>
   <si>
-    <t>04212ea5-bf2c-4cd3-9ce3-1c54a1459b91</t>
-  </si>
-  <si>
-    <t>481d5c9a-fa16-48b0-92ea-db8521764328</t>
-  </si>
-  <si>
     <t>Felipe Dalpino von Scheibler</t>
   </si>
   <si>
     <t>felipe.dalpinovonscheibler@thomsonreuters.com</t>
   </si>
   <si>
+    <t>9f8ff5f2-71e2-4ec6-8ff9-cf2937d6f2ca</t>
+  </si>
+  <si>
+    <t>4d9ac0d1-1776-4fac-b963-bd3cbb651d7f</t>
+  </si>
+  <si>
     <t>6f401251-20ac-480c-be3b-fe158f70e070</t>
   </si>
   <si>
-    <t>Avaliação Modular -  Contabilidade I</t>
+    <t>d447acd6-a654-40a0-bb22-805415667334</t>
   </si>
   <si>
     <t>1087baa0-bb07-40b3-a0a2-d24ca3619640</t>
   </si>
   <si>
-    <t>9f8ff5f2-71e2-4ec6-8ff9-cf2937d6f2ca</t>
-  </si>
-  <si>
-    <t>4d9ac0d1-1776-4fac-b963-bd3cbb651d7f</t>
+    <t>Fernanda Chantre Garcia</t>
+  </si>
+  <si>
+    <t>fernanda.chantregarcia@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>d50d5e0a-5ae5-4929-8f32-76986aa96977</t>
+  </si>
+  <si>
+    <t>9916e041-e2d2-40be-8873-455f0837e124</t>
+  </si>
+  <si>
+    <t>0cabbad3-1f4b-45e1-af4b-494964596505</t>
+  </si>
+  <si>
+    <t>cefcd15a-6607-46c9-be01-feb71c8afb04</t>
+  </si>
+  <si>
+    <t>Fernanda Ramos de Almeida</t>
+  </si>
+  <si>
+    <t>fernanda.ramosdealmeida@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>92442f30-5526-409e-98be-0676a135afe8</t>
+  </si>
+  <si>
+    <t>GESSICA KAKEYA</t>
+  </si>
+  <si>
+    <t>gessica.kakeya@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>2f45c30c-8dc9-429d-ac9b-35a9dfaaab4f</t>
+  </si>
+  <si>
+    <t>86621237-8df6-4ef9-99c0-0e08e5370074</t>
+  </si>
+  <si>
+    <t>Avaliação Modular - Onvio/Processos e Messenger</t>
+  </si>
+  <si>
+    <t>1965b0bf-014c-475e-a88b-ec23d2cb7aee</t>
+  </si>
+  <si>
+    <t>ae39923f-7dd4-45e4-bdee-85cfc6bf344e</t>
+  </si>
+  <si>
+    <t>cda575fa-ff2b-4ff7-bd03-10054a15a324</t>
   </si>
   <si>
     <t>20bc725a-4146-405c-a126-30ec65bb0b19</t>
   </si>
   <si>
-    <t>86621237-8df6-4ef9-99c0-0e08e5370074</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>cda575fa-ff2b-4ff7-bd03-10054a15a324</t>
+    <t>e6383947-4f3f-4863-8763-a392a0afdc23</t>
   </si>
   <si>
     <t>723c274b-ab71-4453-86d8-0af283a15e2a</t>
   </si>
   <si>
+    <t>bceadea9-1e04-43b7-a81e-5a80c0928832</t>
+  </si>
+  <si>
+    <t>2d3e88f0-e94f-49fc-b19b-101d27623207</t>
+  </si>
+  <si>
     <t>1d440a09-79e6-42e4-8fc4-fb3415cd3cbd</t>
   </si>
   <si>
-    <t>bceadea9-1e04-43b7-a81e-5a80c0928832</t>
-  </si>
-  <si>
     <t>2f8f76a1-e71d-43b2-ab6f-835104bf2b1b</t>
   </si>
   <si>
@@ -739,6 +844,15 @@
     <t>a5f33f72-418a-4394-8c42-be8e9e596fe8</t>
   </si>
   <si>
+    <t>James Francis Januario</t>
+  </si>
+  <si>
+    <t>jamesfrancis.januario@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>80a71359-4b9f-4bea-96bd-060dabe8c881</t>
+  </si>
+  <si>
     <t>Jean Carlos</t>
   </si>
   <si>
@@ -748,12 +862,33 @@
     <t>417324d2-9cd3-4f02-b5b6-8947c633c571</t>
   </si>
   <si>
+    <t>Juliana Cugler Valente</t>
+  </si>
+  <si>
+    <t>juliana.cuglervalente@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>d02b093d-89fb-4569-bdee-878c7db7fe55</t>
+  </si>
+  <si>
+    <t>f2bdb873-4a4f-45d8-86cc-72b78bbff29e</t>
+  </si>
+  <si>
+    <t>f60792bb-5e61-4486-8b2c-943919cffdca</t>
+  </si>
+  <si>
     <t>c6fbc07c-3269-4d81-9ab6-5bb28573f688</t>
   </si>
   <si>
     <t>93aaae7c-6d98-43ce-bfa4-4a664271a38a</t>
   </si>
   <si>
+    <t>dc2c4da4-693b-4a87-8ae9-d912fba4fe5b</t>
+  </si>
+  <si>
+    <t>bb6aefcc-c377-43dc-a3fe-7ce46e8173d3</t>
+  </si>
+  <si>
     <t>LEANDRO URBANO</t>
   </si>
   <si>
@@ -763,6 +898,36 @@
     <t>50f3f916-2bcf-43bd-b12d-ca5a68c00744</t>
   </si>
   <si>
+    <t>LEONARDO ANTÔNIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>leonardo.santos@df.softnewss.com.br</t>
+  </si>
+  <si>
+    <t>5e443bf5-77e9-4bdb-8c42-9c654c9d5e2e</t>
+  </si>
+  <si>
+    <t>54fe7b93-4395-48bc-b602-dce01d4681bd</t>
+  </si>
+  <si>
+    <t>Avaliação Modular - Honorários II</t>
+  </si>
+  <si>
+    <t>56813220-f6d0-41a8-a31e-fbde9a207a3a</t>
+  </si>
+  <si>
+    <t>c2d6cb33-1efa-49d9-aac3-0d6c75828590</t>
+  </si>
+  <si>
+    <t>3631442d-f77c-4a3f-9c9e-a1bd8617fecc</t>
+  </si>
+  <si>
+    <t>c2655734-fe23-427f-be56-e9ceda2a925e</t>
+  </si>
+  <si>
+    <t>86ce70f3-f107-4199-9f89-2e63181d5b98</t>
+  </si>
+  <si>
     <t>MAIKO PEREIRA</t>
   </si>
   <si>
@@ -781,6 +946,21 @@
     <t>48284f0b-f2e5-4000-b9e5-ab747a1e77a3</t>
   </si>
   <si>
+    <t>Miriam Pereira</t>
+  </si>
+  <si>
+    <t>miriam.pereira@alpha-sistemas.net</t>
+  </si>
+  <si>
+    <t>141ae669-6464-4d81-b671-a7560cf80f32</t>
+  </si>
+  <si>
+    <t>e27a42ba-f306-4380-adf4-93642bedd15b</t>
+  </si>
+  <si>
+    <t>a0371aae-3422-4b40-9c6a-bd66fdcfbdc8</t>
+  </si>
+  <si>
     <t>Paloma Menezes</t>
   </si>
   <si>
@@ -796,18 +976,21 @@
     <t>pedro.souza2@thomsonreuters.com</t>
   </si>
   <si>
+    <t>ad427d21-3a89-4f0c-901b-9d71749264cc</t>
+  </si>
+  <si>
+    <t>6e9629c4-6bc6-429d-949f-94559285c5f1</t>
+  </si>
+  <si>
     <t>35def769-d955-47b6-afd1-8663fe78ada0</t>
   </si>
   <si>
+    <t>f7230b93-0fca-49e1-ba80-00dd24a48f84</t>
+  </si>
+  <si>
     <t>4ae0377c-9897-48a7-a9f0-ff998c7bd38f</t>
   </si>
   <si>
-    <t>f7230b93-0fca-49e1-ba80-00dd24a48f84</t>
-  </si>
-  <si>
-    <t>ad427d21-3a89-4f0c-901b-9d71749264cc</t>
-  </si>
-  <si>
     <t>RICARDO CAVALLI</t>
   </si>
   <si>
@@ -817,109 +1000,37 @@
     <t>7d309ee1-bdc6-4533-bc06-88be92e8d912</t>
   </si>
   <si>
+    <t>Renata de Oliveira Mendonca</t>
+  </si>
+  <si>
+    <t>renata.deoliveiramendonca@thomsonreuters.com</t>
+  </si>
+  <si>
+    <t>ec780498-0a7d-4c64-9c73-3c721234244c</t>
+  </si>
+  <si>
+    <t>ab118d4c-0d9b-46da-9a8f-cd7d7cc2b743</t>
+  </si>
+  <si>
+    <t>0aa6f13a-1ef5-4a4c-96db-8fa65ba15378</t>
+  </si>
+  <si>
+    <t>a3d6ad28-2c0a-4f0c-a73e-9a35a62073bd</t>
+  </si>
+  <si>
+    <t>b93caca5-b4fb-4459-bb9f-da4d67daa626</t>
+  </si>
+  <si>
     <t>8ec315c1-e0b4-41e9-9e6d-c00aa723b734</t>
   </si>
   <si>
-    <t>b93caca5-b4fb-4459-bb9f-da4d67daa626</t>
-  </si>
-  <si>
     <t>209d6921-cbbc-45b5-9977-4cdf75580790</t>
   </si>
   <si>
-    <t>THIAGO.DOSANTOS@THOMSONREUTERS.COM</t>
-  </si>
-  <si>
-    <t>thiago.dosantos@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>6654c1e6-0b78-4390-9652-6550f0ed1ca6</t>
-  </si>
-  <si>
-    <t>Taynara Silva Serra</t>
-  </si>
-  <si>
-    <t>taynara@harvtec.com.br</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Escrita Fiscal III</t>
-  </si>
-  <si>
-    <t>d915877c-b725-4c70-b50d-7942224d8dc4</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Folha de Pagamento II</t>
-  </si>
-  <si>
-    <t>250382e1-31d5-4dbd-ab42-6eef27dd7b76</t>
-  </si>
-  <si>
-    <t>c8804ed5-565e-4875-bb01-01565f2ab2dd</t>
-  </si>
-  <si>
-    <t>abe64603-bfcd-4f31-9f89-e44283e172fa</t>
-  </si>
-  <si>
-    <t>Thiago Canabrava</t>
-  </si>
-  <si>
-    <t>thiago.canabrava@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>3fbf4055-3246-439c-8154-a20e7f63d22d</t>
-  </si>
-  <si>
-    <t>Victor Bonfim</t>
-  </si>
-  <si>
-    <t>victor.bonfim@teknorte.com.br</t>
-  </si>
-  <si>
-    <t>fde8c019-d349-4c21-9528-ca8c2fd4c65a</t>
-  </si>
-  <si>
-    <t>bc1acfc3-f1d3-4d65-9e1f-5dc0616242ef</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Folha de Pagamento III</t>
-  </si>
-  <si>
-    <t>e975808e-cf33-4e79-9c26-a67d0f46c107</t>
-  </si>
-  <si>
-    <t>Avaliação Modular - Escrita Fiscal II</t>
-  </si>
-  <si>
-    <t>bd4eaed9-7c2f-476a-a5e5-ac8aad17bd40</t>
-  </si>
-  <si>
-    <t>b023668e-9391-492f-a842-da837b30033b</t>
-  </si>
-  <si>
-    <t>918a7775-68d2-4b7f-886d-83f5f8b4bb93</t>
-  </si>
-  <si>
-    <t>b00300c0-48c7-4217-a079-1f4a32b86a98</t>
-  </si>
-  <si>
-    <t>31b69f31-ee77-4628-865a-e8c59b6b0b2f</t>
-  </si>
-  <si>
-    <t>andressa.rodrigues@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>cbd1a72b-60b4-432a-934c-97c2ab9d7755</t>
-  </si>
-  <si>
-    <t>fernando.biudecarvalho@thomsonreuters.com</t>
-  </si>
-  <si>
-    <t>c5e39465-7826-400c-83e6-e676afa64966</t>
-  </si>
-  <si>
-    <t>paulo.andrade@2bst.com.br</t>
-  </si>
-  <si>
-    <t>7aa81039-c142-4a57-b76f-068fc2985942</t>
+    <t>48c3c5ab-be40-41fb-9e0c-fc1e75ddc72b</t>
+  </si>
+  <si>
+    <t>4a94a277-ccc0-4f1c-be4f-80dffe4e6203</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1671,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>6033759</v>
@@ -1576,10 +1687,10 @@
       </c>
       <c r="H6" s="1"/>
       <c r="L6">
-        <v>1724163</v>
+        <v>1723203</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N6" s="2">
         <v>46244</v>
@@ -1588,24 +1699,24 @@
         <v>46244</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="s">
         <v>20</v>
       </c>
       <c r="R6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S6" t="s">
         <v>20</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7">
         <v>6033759</v>
@@ -1621,10 +1732,10 @@
       </c>
       <c r="H7" s="1"/>
       <c r="L7">
-        <v>1723203</v>
+        <v>1724178</v>
       </c>
       <c r="M7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N7" s="2">
         <v>46244</v>
@@ -1639,18 +1750,18 @@
         <v>20</v>
       </c>
       <c r="R7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S7" t="s">
         <v>20</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8">
         <v>6033759</v>
@@ -1666,10 +1777,10 @@
       </c>
       <c r="H8" s="1"/>
       <c r="L8">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N8" s="2">
         <v>46244</v>
@@ -1678,13 +1789,13 @@
         <v>46244</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="s">
         <v>20</v>
       </c>
       <c r="R8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S8" t="s">
         <v>20</v>
@@ -1695,23 +1806,23 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <v>6702264</v>
       </c>
       <c r="C9" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="H9" s="1"/>
       <c r="L9">
         <v>1706681</v>
       </c>
       <c r="M9" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="N9" s="2">
         <v>46217</v>
@@ -1726,7 +1837,7 @@
         <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="S9" t="s">
         <v>20</v>
@@ -1737,19 +1848,19 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>6453878</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="H10" s="1"/>
       <c r="L10">
@@ -1771,7 +1882,7 @@
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="S10" t="s">
         <v>20</v>
@@ -1782,7 +1893,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B11">
         <v>3368423</v>
@@ -1827,19 +1938,19 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <v>3369467</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E12" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="H12" s="1"/>
       <c r="L12">
@@ -1861,7 +1972,7 @@
         <v>20</v>
       </c>
       <c r="R12" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="S12" t="s">
         <v>20</v>
@@ -1872,74 +1983,77 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B13">
-        <v>6192692</v>
+        <v>3391750</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>179</v>
+      </c>
+      <c r="E13" t="s">
+        <v>179</v>
       </c>
       <c r="H13" s="1"/>
       <c r="L13">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N13" s="2">
-        <v>46238</v>
+        <v>46308</v>
       </c>
       <c r="O13" s="2">
-        <v>46238</v>
+        <v>46308</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q13" t="s">
         <v>20</v>
       </c>
       <c r="R13" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="S13" t="s">
         <v>20</v>
       </c>
       <c r="T13">
-        <v>58</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B14">
-        <v>6159220</v>
+        <v>3391750</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="H14" s="1"/>
       <c r="L14">
-        <v>1724163</v>
+        <v>1723203</v>
       </c>
       <c r="M14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N14" s="2">
-        <v>46240</v>
+        <v>46308</v>
       </c>
       <c r="O14" s="2">
-        <v>46240</v>
+        <v>46308</v>
       </c>
       <c r="P14">
         <v>90</v>
@@ -1948,27 +2062,30 @@
         <v>20</v>
       </c>
       <c r="R14" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="S14" t="s">
         <v>20</v>
       </c>
       <c r="T14">
-        <v>2690</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15">
-        <v>5432812</v>
+        <v>3391750</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>179</v>
+      </c>
+      <c r="E15" t="s">
+        <v>179</v>
       </c>
       <c r="H15" s="1"/>
       <c r="L15">
@@ -1978,55 +2095,52 @@
         <v>33</v>
       </c>
       <c r="N15" s="2">
-        <v>46245</v>
+        <v>46308</v>
       </c>
       <c r="O15" s="2">
-        <v>46245</v>
+        <v>46308</v>
       </c>
       <c r="P15">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="s">
         <v>20</v>
       </c>
       <c r="R15" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="S15" t="s">
         <v>20</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16">
-        <v>6222316</v>
+        <v>6192692</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H16" s="1"/>
       <c r="L16">
-        <v>1723203</v>
+        <v>1724163</v>
       </c>
       <c r="M16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N16" s="2">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="O16" s="2">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -2035,30 +2149,30 @@
         <v>20</v>
       </c>
       <c r="R16" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="S16" t="s">
         <v>20</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17">
-        <v>3391206</v>
+        <v>7318794</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="H17" s="1"/>
       <c r="L17">
@@ -2068,145 +2182,142 @@
         <v>33</v>
       </c>
       <c r="N17" s="2">
-        <v>46237</v>
+        <v>46282</v>
       </c>
       <c r="O17" s="2">
-        <v>46237</v>
+        <v>46282</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="s">
         <v>20</v>
       </c>
       <c r="R17" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="S17" t="s">
         <v>20</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B18">
-        <v>3797742</v>
+        <v>6159220</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H18" s="1"/>
       <c r="L18">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N18" s="2">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="O18" s="2">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q18" t="s">
         <v>20</v>
       </c>
       <c r="R18" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="S18" t="s">
         <v>20</v>
       </c>
       <c r="T18">
-        <v>1765</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B19">
-        <v>6091089</v>
+        <v>5432812</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="H19" s="1"/>
       <c r="L19">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M19" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N19" s="2">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="O19" s="2">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="P19">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
       <c r="R19" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="S19" t="s">
         <v>20</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B20">
-        <v>6433541</v>
+        <v>6222316</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H20" s="1"/>
       <c r="L20">
-        <v>1724163</v>
+        <v>1723203</v>
       </c>
       <c r="M20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N20" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="O20" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -2215,30 +2326,30 @@
         <v>20</v>
       </c>
       <c r="R20" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="S20" t="s">
         <v>20</v>
       </c>
       <c r="T20">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B21">
-        <v>6386086</v>
+        <v>3391206</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H21" s="1"/>
       <c r="L21">
@@ -2248,42 +2359,42 @@
         <v>33</v>
       </c>
       <c r="N21" s="2">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="O21" s="2">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="s">
         <v>20</v>
       </c>
       <c r="R21" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="S21" t="s">
         <v>20</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B22">
-        <v>3371119</v>
+        <v>3797742</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H22" s="1"/>
       <c r="L22">
@@ -2293,10 +2404,10 @@
         <v>40</v>
       </c>
       <c r="N22" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="O22" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -2305,265 +2416,268 @@
         <v>20</v>
       </c>
       <c r="R22" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="S22" t="s">
         <v>20</v>
       </c>
       <c r="T22">
-        <v>26</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B23">
-        <v>3369232</v>
+        <v>7208225</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="H23" s="1"/>
       <c r="L23">
-        <v>1724178</v>
+        <v>1706681</v>
       </c>
       <c r="M23" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="N23" s="2">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="O23" s="2">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q23" t="s">
         <v>20</v>
       </c>
       <c r="R23" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="S23" t="s">
         <v>20</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B24">
-        <v>3878447</v>
+        <v>3394410</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H24" s="1"/>
       <c r="L24">
-        <v>1724178</v>
+        <v>1708464</v>
       </c>
       <c r="M24" t="s">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="N24" s="2">
-        <v>46244</v>
+        <v>46290</v>
       </c>
       <c r="O24" s="2">
-        <v>46244</v>
+        <v>46290</v>
       </c>
       <c r="P24">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="Q24" t="s">
         <v>20</v>
       </c>
       <c r="R24" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="S24" t="s">
         <v>20</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B25">
-        <v>3395015</v>
+        <v>7270971</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D25" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="H25" s="1"/>
       <c r="L25">
-        <v>1708464</v>
+        <v>1706681</v>
       </c>
       <c r="M25" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2">
-        <v>46211</v>
+        <v>46280</v>
       </c>
       <c r="O25" s="2">
-        <v>46211</v>
+        <v>46280</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="Q25" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R25" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S25" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B26">
-        <v>3395015</v>
+        <v>7270971</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D26" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="H26" s="1"/>
       <c r="L26">
-        <v>1724178</v>
+        <v>1706681</v>
       </c>
       <c r="M26" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="N26" s="2">
-        <v>46245</v>
+        <v>46280</v>
       </c>
       <c r="O26" s="2">
-        <v>46245</v>
+        <v>46280</v>
       </c>
       <c r="P26">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="Q26" t="s">
         <v>20</v>
       </c>
       <c r="R26" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="S26" t="s">
         <v>20</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B27">
-        <v>6429182</v>
+        <v>7270971</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E27" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="H27" s="1"/>
       <c r="L27">
-        <v>1724163</v>
+        <v>1708464</v>
       </c>
       <c r="M27" t="s">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="N27" s="2">
-        <v>46245</v>
+        <v>46275</v>
       </c>
       <c r="O27" s="2">
-        <v>46245</v>
+        <v>46275</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q27" t="s">
         <v>20</v>
       </c>
       <c r="R27" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="S27" t="s">
         <v>20</v>
       </c>
       <c r="T27">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B28">
-        <v>5345301</v>
+        <v>7270971</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>213</v>
+        <v>197</v>
+      </c>
+      <c r="E28" t="s">
+        <v>197</v>
       </c>
       <c r="H28" s="1"/>
       <c r="L28">
-        <v>1724163</v>
+        <v>1710979</v>
       </c>
       <c r="M28" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="N28" s="2">
-        <v>46244</v>
+        <v>46280</v>
       </c>
       <c r="O28" s="2">
-        <v>46244</v>
+        <v>46280</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -2572,322 +2686,313 @@
         <v>20</v>
       </c>
       <c r="R28" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="S28" t="s">
         <v>20</v>
       </c>
       <c r="T28">
-        <v>13</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B29">
-        <v>6232612</v>
+        <v>7270971</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="H29" s="1"/>
       <c r="L29">
-        <v>1723203</v>
+        <v>1711329</v>
       </c>
       <c r="M29" t="s">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="N29" s="2">
-        <v>46238</v>
+        <v>46276</v>
       </c>
       <c r="O29" s="2">
-        <v>46238</v>
+        <v>46276</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q29" t="s">
         <v>20</v>
       </c>
       <c r="R29" t="s">
-        <v>94</v>
+        <v>204</v>
       </c>
       <c r="S29" t="s">
         <v>20</v>
       </c>
       <c r="T29">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B30">
-        <v>3377344</v>
+        <v>6091089</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H30" s="1"/>
-      <c r="J30" t="s">
-        <v>32</v>
-      </c>
       <c r="L30">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M30" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N30" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="O30" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="Q30" t="s">
         <v>20</v>
       </c>
       <c r="R30" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="S30" t="s">
         <v>20</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="B31">
-        <v>6232614</v>
+        <v>7318792</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D31" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E31" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="H31" s="1"/>
       <c r="L31">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M31" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N31" s="2">
-        <v>46244</v>
+        <v>46282</v>
       </c>
       <c r="O31" s="2">
-        <v>46244</v>
+        <v>46282</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q31" t="s">
         <v>20</v>
       </c>
       <c r="R31" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="S31" t="s">
         <v>20</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B32">
-        <v>6232614</v>
+        <v>7218730</v>
       </c>
       <c r="C32" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="H32" s="1"/>
       <c r="L32">
-        <v>1724163</v>
+        <v>1706681</v>
       </c>
       <c r="M32" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="N32" s="2">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="O32" s="2">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="P32">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Q32" t="s">
         <v>20</v>
       </c>
       <c r="R32" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="S32" t="s">
         <v>20</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B33">
-        <v>6232614</v>
+        <v>7218730</v>
       </c>
       <c r="C33" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D33" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E33" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="H33" s="1"/>
       <c r="L33">
-        <v>1723203</v>
+        <v>1711329</v>
       </c>
       <c r="M33" t="s">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="N33" s="2">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="O33" s="2">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="P33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q33" t="s">
         <v>20</v>
       </c>
       <c r="R33" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="S33" t="s">
         <v>20</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="B34">
-        <v>4543344</v>
+        <v>7218730</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>208</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>209</v>
+      </c>
+      <c r="E34" t="s">
+        <v>209</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="I34" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" t="s">
-        <v>32</v>
-      </c>
       <c r="L34">
-        <v>1724178</v>
+        <v>1710979</v>
       </c>
       <c r="M34" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="N34" s="2">
-        <v>46241</v>
+        <v>46254</v>
       </c>
       <c r="O34" s="2">
-        <v>46241</v>
+        <v>46254</v>
       </c>
       <c r="P34">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="s">
         <v>20</v>
       </c>
       <c r="R34" t="s">
-        <v>99</v>
+        <v>212</v>
       </c>
       <c r="S34" t="s">
         <v>20</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="B35">
-        <v>3377347</v>
+        <v>7218730</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="H35" s="1"/>
       <c r="L35">
-        <v>1724178</v>
+        <v>1723203</v>
       </c>
       <c r="M35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N35" s="2">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="O35" s="2">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -2896,52 +3001,52 @@
         <v>20</v>
       </c>
       <c r="R35" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="S35" t="s">
         <v>20</v>
       </c>
       <c r="T35">
-        <v>5242</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="B36">
-        <v>7138413</v>
+        <v>7218730</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="E36" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H36" s="1"/>
       <c r="L36">
         <v>1708464</v>
       </c>
       <c r="M36" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="O36" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="P36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q36" t="s">
         <v>20</v>
       </c>
       <c r="R36" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="S36" t="s">
         <v>20</v>
@@ -2952,154 +3057,154 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="B37">
-        <v>7138413</v>
+        <v>6433541</v>
       </c>
       <c r="C37" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="H37" s="1"/>
       <c r="L37">
-        <v>1711329</v>
+        <v>1724163</v>
       </c>
       <c r="M37" t="s">
-        <v>223</v>
+        <v>33</v>
       </c>
       <c r="N37" s="2">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="O37" s="2">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="P37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q37" t="s">
         <v>20</v>
       </c>
       <c r="R37" t="s">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s">
         <v>20</v>
       </c>
       <c r="T37">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="B38">
-        <v>7138413</v>
+        <v>6386086</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="H38" s="1"/>
       <c r="L38">
-        <v>1723203</v>
+        <v>1724163</v>
       </c>
       <c r="M38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N38" s="2">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="O38" s="2">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q38" t="s">
         <v>20</v>
       </c>
       <c r="R38" t="s">
-        <v>225</v>
+        <v>85</v>
       </c>
       <c r="S38" t="s">
         <v>20</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="B39">
-        <v>7138413</v>
+        <v>7318789</v>
       </c>
       <c r="C39" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D39" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E39" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H39" s="1"/>
       <c r="L39">
-        <v>1706681</v>
+        <v>1724163</v>
       </c>
       <c r="M39" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="N39" s="2">
-        <v>46247</v>
+        <v>46282</v>
       </c>
       <c r="O39" s="2">
-        <v>46247</v>
+        <v>46282</v>
       </c>
       <c r="P39">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q39" t="s">
         <v>20</v>
       </c>
       <c r="R39" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="S39" t="s">
         <v>20</v>
       </c>
       <c r="T39">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="B40">
-        <v>3377007</v>
+        <v>3371119</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H40" s="1"/>
       <c r="L40">
@@ -3109,10 +3214,10 @@
         <v>40</v>
       </c>
       <c r="N40" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O40" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="P40">
         <v>100</v>
@@ -3121,30 +3226,30 @@
         <v>20</v>
       </c>
       <c r="R40" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="S40" t="s">
         <v>20</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B41">
-        <v>3367693</v>
+        <v>3369232</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H41" s="1"/>
       <c r="L41">
@@ -3154,10 +3259,10 @@
         <v>40</v>
       </c>
       <c r="N41" s="2">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="O41" s="2">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="P41">
         <v>100</v>
@@ -3166,30 +3271,30 @@
         <v>20</v>
       </c>
       <c r="R41" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="S41" t="s">
         <v>20</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="B42">
-        <v>3371022</v>
+        <v>3878447</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="E42" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="H42" s="1"/>
       <c r="L42">
@@ -3199,220 +3304,196 @@
         <v>40</v>
       </c>
       <c r="N42" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="O42" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="P42">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q42" t="s">
         <v>20</v>
       </c>
       <c r="R42" t="s">
-        <v>111</v>
+        <v>220</v>
       </c>
       <c r="S42" t="s">
         <v>20</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B43">
-        <v>7031896</v>
+        <v>3395015</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="H43" s="1"/>
-      <c r="J43" t="s">
-        <v>23</v>
-      </c>
       <c r="L43">
-        <v>1711329</v>
+        <v>1724178</v>
       </c>
       <c r="M43" t="s">
+        <v>40</v>
+      </c>
+      <c r="N43" s="2">
+        <v>46245</v>
+      </c>
+      <c r="O43" s="2">
+        <v>46245</v>
+      </c>
+      <c r="P43">
+        <v>80</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>20</v>
+      </c>
+      <c r="R43" t="s">
         <v>223</v>
       </c>
-      <c r="N43" s="2">
-        <v>46213</v>
-      </c>
-      <c r="O43" s="2">
-        <v>46213</v>
-      </c>
-      <c r="P43">
-        <v>90</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>20</v>
-      </c>
-      <c r="R43" t="s">
-        <v>227</v>
-      </c>
       <c r="S43" t="s">
         <v>20</v>
       </c>
       <c r="T43">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B44">
-        <v>7031896</v>
+        <v>3395015</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="E44" t="s">
-        <v>22</v>
-      </c>
-      <c r="G44" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="H44" s="1"/>
-      <c r="J44" t="s">
-        <v>23</v>
-      </c>
       <c r="L44">
-        <v>1724163</v>
+        <v>1708464</v>
       </c>
       <c r="M44" t="s">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2">
-        <v>46238</v>
+        <v>46211</v>
       </c>
       <c r="O44" s="2">
-        <v>46238</v>
+        <v>46211</v>
       </c>
       <c r="P44">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q44" t="s">
         <v>20</v>
       </c>
       <c r="R44" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
       <c r="S44" t="s">
         <v>20</v>
       </c>
       <c r="T44">
-        <v>1042</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="B45">
-        <v>7031896</v>
+        <v>6429182</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" t="s">
-        <v>112</v>
+        <v>226</v>
       </c>
       <c r="H45" s="1"/>
-      <c r="J45" t="s">
-        <v>23</v>
-      </c>
       <c r="L45">
-        <v>1708464</v>
+        <v>1724163</v>
       </c>
       <c r="M45" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="N45" s="2">
-        <v>46211</v>
+        <v>46245</v>
       </c>
       <c r="O45" s="2">
-        <v>46211</v>
+        <v>46245</v>
       </c>
       <c r="P45">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q45" t="s">
         <v>20</v>
       </c>
       <c r="R45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S45" t="s">
         <v>20</v>
       </c>
       <c r="T45">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="B46">
-        <v>7031896</v>
+        <v>6205953</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" t="s">
-        <v>112</v>
+        <v>229</v>
       </c>
       <c r="H46" s="1"/>
-      <c r="J46" t="s">
-        <v>23</v>
-      </c>
       <c r="L46">
-        <v>1706681</v>
+        <v>1710979</v>
       </c>
       <c r="M46" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="N46" s="2">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="O46" s="2">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="P46">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="Q46" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="R46" t="s">
         <v>230</v>
@@ -3421,236 +3502,209 @@
         <v>20</v>
       </c>
       <c r="T46">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B47">
-        <v>7031895</v>
+        <v>5345301</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>231</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="H47" s="1"/>
-      <c r="J47" t="s">
-        <v>23</v>
-      </c>
       <c r="L47">
-        <v>1708464</v>
+        <v>1724163</v>
       </c>
       <c r="M47" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="N47" s="2">
-        <v>46211</v>
+        <v>46244</v>
       </c>
       <c r="O47" s="2">
-        <v>46211</v>
+        <v>46244</v>
       </c>
       <c r="P47">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q47" t="s">
         <v>20</v>
       </c>
       <c r="R47" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S47" t="s">
         <v>20</v>
       </c>
       <c r="T47">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="B48">
-        <v>7031895</v>
+        <v>6232612</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G48" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="H48" s="1"/>
-      <c r="J48" t="s">
-        <v>23</v>
-      </c>
       <c r="L48">
-        <v>1706681</v>
+        <v>1723203</v>
       </c>
       <c r="M48" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="N48" s="2">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="O48" s="2">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="P48">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="Q48" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="R48" t="s">
-        <v>232</v>
+        <v>94</v>
       </c>
       <c r="S48" t="s">
         <v>20</v>
       </c>
       <c r="T48">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B49">
-        <v>7031895</v>
+        <v>3377344</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H49" s="1"/>
       <c r="J49" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L49">
-        <v>1711329</v>
+        <v>1724163</v>
       </c>
       <c r="M49" t="s">
-        <v>223</v>
+        <v>33</v>
       </c>
       <c r="N49" s="2">
-        <v>46213</v>
+        <v>46237</v>
       </c>
       <c r="O49" s="2">
-        <v>46213</v>
+        <v>46237</v>
       </c>
       <c r="P49">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q49" t="s">
         <v>20</v>
       </c>
       <c r="R49" t="s">
-        <v>233</v>
+        <v>34</v>
       </c>
       <c r="S49" t="s">
         <v>20</v>
       </c>
       <c r="T49">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B50">
-        <v>7031895</v>
+        <v>6232614</v>
       </c>
       <c r="C50" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" t="s">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="H50" s="1"/>
-      <c r="J50" t="s">
-        <v>23</v>
-      </c>
       <c r="L50">
-        <v>1706681</v>
+        <v>1723203</v>
       </c>
       <c r="M50" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="N50" s="2">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="O50" s="2">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="P50">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Q50" t="s">
         <v>20</v>
       </c>
       <c r="R50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S50" t="s">
         <v>20</v>
       </c>
       <c r="T50">
-        <v>28480</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B51">
-        <v>7031895</v>
+        <v>6232614</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" t="s">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="H51" s="1"/>
-      <c r="J51" t="s">
-        <v>23</v>
-      </c>
       <c r="L51">
         <v>1724163</v>
       </c>
@@ -3658,10 +3712,10 @@
         <v>33</v>
       </c>
       <c r="N51" s="2">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="O51" s="2">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="P51">
         <v>90</v>
@@ -3670,7 +3724,7 @@
         <v>20</v>
       </c>
       <c r="R51" t="s">
-        <v>42</v>
+        <v>237</v>
       </c>
       <c r="S51" t="s">
         <v>20</v>
@@ -3681,77 +3735,80 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B52">
-        <v>6345154</v>
+        <v>6232614</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="D52" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="E52" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="H52" s="1"/>
       <c r="L52">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M52" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N52" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="O52" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="P52">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q52" t="s">
         <v>20</v>
       </c>
       <c r="R52" t="s">
-        <v>116</v>
+        <v>238</v>
       </c>
       <c r="S52" t="s">
         <v>20</v>
       </c>
       <c r="T52">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B53">
-        <v>6386085</v>
+        <v>4543344</v>
       </c>
       <c r="C53" t="s">
-        <v>235</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>236</v>
-      </c>
-      <c r="E53" t="s">
-        <v>236</v>
+        <v>97</v>
       </c>
       <c r="H53" s="1"/>
+      <c r="I53" t="s">
+        <v>98</v>
+      </c>
+      <c r="J53" t="s">
+        <v>32</v>
+      </c>
       <c r="L53">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M53" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N53" s="2">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="O53" s="2">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="P53">
         <v>90</v>
@@ -3760,7 +3817,7 @@
         <v>20</v>
       </c>
       <c r="R53" t="s">
-        <v>237</v>
+        <v>99</v>
       </c>
       <c r="S53" t="s">
         <v>20</v>
@@ -3771,19 +3828,19 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B54">
-        <v>3370070</v>
+        <v>3377347</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H54" s="1"/>
       <c r="L54">
@@ -3793,10 +3850,10 @@
         <v>40</v>
       </c>
       <c r="N54" s="2">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="O54" s="2">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="P54">
         <v>100</v>
@@ -3805,43 +3862,43 @@
         <v>20</v>
       </c>
       <c r="R54" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="S54" t="s">
         <v>20</v>
       </c>
       <c r="T54">
-        <v>15</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B55">
-        <v>3367914</v>
+        <v>7138413</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="E55" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="H55" s="1"/>
       <c r="L55">
-        <v>1724163</v>
+        <v>1723203</v>
       </c>
       <c r="M55" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N55" s="2">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O55" s="2">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="P55">
         <v>100</v>
@@ -3850,40 +3907,43 @@
         <v>20</v>
       </c>
       <c r="R55" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="S55" t="s">
         <v>20</v>
       </c>
       <c r="T55">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B56">
-        <v>4745431</v>
+        <v>7138413</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>240</v>
+      </c>
+      <c r="E56" t="s">
+        <v>240</v>
       </c>
       <c r="H56" s="1"/>
       <c r="L56">
-        <v>1724163</v>
+        <v>1706681</v>
       </c>
       <c r="M56" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="N56" s="2">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="O56" s="2">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="P56">
         <v>100</v>
@@ -3892,438 +3952,435 @@
         <v>20</v>
       </c>
       <c r="R56" t="s">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="S56" t="s">
         <v>20</v>
       </c>
       <c r="T56">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B57">
-        <v>6222314</v>
+        <v>7138413</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="H57" s="1"/>
       <c r="L57">
-        <v>1723203</v>
+        <v>1708464</v>
       </c>
       <c r="M57" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="N57" s="2">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="O57" s="2">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="P57">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q57" t="s">
         <v>20</v>
       </c>
       <c r="R57" t="s">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="S57" t="s">
         <v>20</v>
       </c>
       <c r="T57">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B58">
-        <v>3394648</v>
+        <v>7138413</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="E58" t="s">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="H58" s="1"/>
       <c r="L58">
-        <v>1724178</v>
+        <v>1710979</v>
       </c>
       <c r="M58" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="N58" s="2">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="O58" s="2">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="P58">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q58" t="s">
         <v>20</v>
       </c>
       <c r="R58" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="S58" t="s">
         <v>20</v>
       </c>
       <c r="T58">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B59">
-        <v>3797743</v>
+        <v>7138413</v>
       </c>
       <c r="C59" t="s">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="D59" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="E59" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="H59" s="1"/>
-      <c r="K59" t="s">
-        <v>134</v>
-      </c>
       <c r="L59">
-        <v>1724163</v>
+        <v>1711329</v>
       </c>
       <c r="M59" t="s">
-        <v>33</v>
+        <v>203</v>
       </c>
       <c r="N59" s="2">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O59" s="2">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="P59">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q59" t="s">
         <v>20</v>
       </c>
       <c r="R59" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="S59" t="s">
         <v>20</v>
       </c>
       <c r="T59">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B60">
-        <v>6429181</v>
+        <v>7364997</v>
       </c>
       <c r="C60" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E60" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H60" s="1"/>
       <c r="L60">
-        <v>1724163</v>
+        <v>1706681</v>
       </c>
       <c r="M60" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="N60" s="2">
-        <v>46244</v>
+        <v>46303</v>
       </c>
       <c r="O60" s="2">
-        <v>46244</v>
+        <v>46303</v>
       </c>
       <c r="P60">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="Q60" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R60" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="S60" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T60">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="B61">
-        <v>3406205</v>
+        <v>7364997</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="E61" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="H61" s="1"/>
       <c r="L61">
-        <v>1724163</v>
+        <v>1706681</v>
       </c>
       <c r="M61" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="N61" s="2">
-        <v>46237</v>
+        <v>46308</v>
       </c>
       <c r="O61" s="2">
-        <v>46237</v>
+        <v>46308</v>
       </c>
       <c r="P61">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q61" t="s">
         <v>20</v>
       </c>
       <c r="R61" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
       <c r="S61" t="s">
         <v>20</v>
       </c>
       <c r="T61">
-        <v>7271</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="B62">
-        <v>3406205</v>
+        <v>7364997</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="E62" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="H62" s="1"/>
       <c r="L62">
-        <v>1706681</v>
+        <v>1711329</v>
       </c>
       <c r="M62" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="N62" s="2">
-        <v>46218</v>
+        <v>46302</v>
       </c>
       <c r="O62" s="2">
-        <v>46218</v>
+        <v>46302</v>
       </c>
       <c r="P62">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q62" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="R62" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="S62" t="s">
         <v>20</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63">
+        <v>214</v>
+      </c>
+      <c r="B63">
+        <v>7364997</v>
+      </c>
+      <c r="C63" t="s">
         <v>246</v>
       </c>
-      <c r="B63">
-        <v>3406205</v>
-      </c>
-      <c r="C63" t="s">
-        <v>136</v>
-      </c>
       <c r="D63" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="E63" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="H63" s="1"/>
       <c r="L63">
-        <v>1724178</v>
+        <v>1710979</v>
       </c>
       <c r="M63" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="N63" s="2">
-        <v>46237</v>
+        <v>46308</v>
       </c>
       <c r="O63" s="2">
-        <v>46237</v>
+        <v>46308</v>
       </c>
       <c r="P63">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q63" t="s">
         <v>20</v>
       </c>
       <c r="R63" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="S63" t="s">
         <v>20</v>
       </c>
       <c r="T63">
-        <v>7259</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64">
+        <v>215</v>
+      </c>
+      <c r="B64">
+        <v>7364997</v>
+      </c>
+      <c r="C64" t="s">
+        <v>246</v>
+      </c>
+      <c r="D64" t="s">
         <v>247</v>
       </c>
-      <c r="B64">
-        <v>3406205</v>
-      </c>
-      <c r="C64" t="s">
-        <v>136</v>
-      </c>
-      <c r="D64" t="s">
-        <v>137</v>
-      </c>
       <c r="E64" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="H64" s="1"/>
       <c r="L64">
-        <v>1723203</v>
+        <v>1708464</v>
       </c>
       <c r="M64" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="N64" s="2">
-        <v>46237</v>
+        <v>46302</v>
       </c>
       <c r="O64" s="2">
-        <v>46237</v>
+        <v>46302</v>
       </c>
       <c r="P64">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q64" t="s">
         <v>20</v>
       </c>
       <c r="R64" t="s">
-        <v>138</v>
+        <v>251</v>
       </c>
       <c r="S64" t="s">
         <v>20</v>
       </c>
       <c r="T64">
-        <v>7350</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="B65">
-        <v>3406205</v>
+        <v>7318793</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="H65" s="1"/>
       <c r="L65">
-        <v>1708464</v>
+        <v>1724163</v>
       </c>
       <c r="M65" t="s">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="N65" s="2">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="O65" s="2">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="P65">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q65" t="s">
         <v>20</v>
       </c>
       <c r="R65" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="S65" t="s">
         <v>20</v>
       </c>
       <c r="T65">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="B66">
-        <v>3384439</v>
+        <v>3377007</v>
       </c>
       <c r="C66" t="s">
-        <v>243</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
-        <v>244</v>
+        <v>104</v>
       </c>
       <c r="E66" t="s">
-        <v>244</v>
+        <v>104</v>
       </c>
       <c r="H66" s="1"/>
       <c r="L66">
@@ -4333,19 +4390,19 @@
         <v>40</v>
       </c>
       <c r="N66" s="2">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="O66" s="2">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="P66">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q66" t="s">
         <v>20</v>
       </c>
       <c r="R66" t="s">
-        <v>245</v>
+        <v>105</v>
       </c>
       <c r="S66" t="s">
         <v>20</v>
@@ -4356,19 +4413,19 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="B67">
-        <v>3379507</v>
+        <v>3367693</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="E67" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="H67" s="1"/>
       <c r="L67">
@@ -4378,10 +4435,10 @@
         <v>40</v>
       </c>
       <c r="N67" s="2">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="O67" s="2">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="P67">
         <v>100</v>
@@ -4390,43 +4447,43 @@
         <v>20</v>
       </c>
       <c r="R67" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="S67" t="s">
         <v>20</v>
       </c>
       <c r="T67">
-        <v>1390</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="B68">
-        <v>3369242</v>
+        <v>3409105</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
+        <v>255</v>
       </c>
       <c r="D68" t="s">
-        <v>145</v>
+        <v>256</v>
       </c>
       <c r="E68" t="s">
-        <v>145</v>
+        <v>256</v>
       </c>
       <c r="H68" s="1"/>
       <c r="L68">
-        <v>1724163</v>
+        <v>1723203</v>
       </c>
       <c r="M68" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N68" s="2">
-        <v>46243</v>
+        <v>46269</v>
       </c>
       <c r="O68" s="2">
-        <v>46243</v>
+        <v>46269</v>
       </c>
       <c r="P68">
         <v>100</v>
@@ -4435,37 +4492,37 @@
         <v>20</v>
       </c>
       <c r="R68" t="s">
-        <v>146</v>
+        <v>257</v>
       </c>
       <c r="S68" t="s">
         <v>20</v>
       </c>
       <c r="T68">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c r="B69">
-        <v>6921313</v>
+        <v>3371022</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="E69" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="H69" s="1"/>
       <c r="L69">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M69" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N69" s="2">
         <v>46241</v>
@@ -4474,139 +4531,157 @@
         <v>46241</v>
       </c>
       <c r="P69">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q69" t="s">
         <v>20</v>
       </c>
       <c r="R69" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="S69" t="s">
         <v>20</v>
       </c>
       <c r="T69">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>307</v>
+        <v>232</v>
       </c>
       <c r="B70">
-        <v>3377340</v>
+        <v>7031896</v>
       </c>
       <c r="C70" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>247</v>
+        <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>247</v>
+        <v>22</v>
+      </c>
+      <c r="G70" t="s">
+        <v>112</v>
       </c>
       <c r="H70" s="1"/>
+      <c r="J70" t="s">
+        <v>23</v>
+      </c>
       <c r="L70">
-        <v>1724178</v>
+        <v>1708464</v>
       </c>
       <c r="M70" t="s">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="N70" s="2">
-        <v>46245</v>
+        <v>46211</v>
       </c>
       <c r="O70" s="2">
-        <v>46245</v>
+        <v>46211</v>
       </c>
       <c r="P70">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q70" t="s">
         <v>20</v>
       </c>
       <c r="R70" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="S70" t="s">
         <v>20</v>
       </c>
       <c r="T70">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>308</v>
+        <v>233</v>
       </c>
       <c r="B71">
-        <v>3419303</v>
+        <v>7031896</v>
       </c>
       <c r="C71" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="E71" t="s">
-        <v>250</v>
+        <v>22</v>
+      </c>
+      <c r="G71" t="s">
+        <v>112</v>
       </c>
       <c r="H71" s="1"/>
+      <c r="J71" t="s">
+        <v>23</v>
+      </c>
       <c r="L71">
-        <v>1724163</v>
+        <v>1715169</v>
       </c>
       <c r="M71" t="s">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="N71" s="2">
-        <v>46244</v>
+        <v>46217</v>
       </c>
       <c r="O71" s="2">
-        <v>46244</v>
+        <v>46217</v>
       </c>
       <c r="P71">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="Q71" t="s">
         <v>20</v>
       </c>
       <c r="R71" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="S71" t="s">
         <v>20</v>
       </c>
       <c r="T71">
-        <v>7</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="B72">
-        <v>3377339</v>
+        <v>7031896</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="E72" t="s">
-        <v>151</v>
+        <v>22</v>
+      </c>
+      <c r="G72" t="s">
+        <v>112</v>
       </c>
       <c r="H72" s="1"/>
+      <c r="J72" t="s">
+        <v>23</v>
+      </c>
       <c r="L72">
-        <v>1724178</v>
+        <v>1710979</v>
       </c>
       <c r="M72" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="N72" s="2">
-        <v>46241</v>
+        <v>46216</v>
       </c>
       <c r="O72" s="2">
-        <v>46241</v>
+        <v>46216</v>
       </c>
       <c r="P72">
         <v>100</v>
@@ -4615,43 +4690,49 @@
         <v>20</v>
       </c>
       <c r="R72" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="S72" t="s">
         <v>20</v>
       </c>
       <c r="T72">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>319</v>
+        <v>235</v>
       </c>
       <c r="B73">
-        <v>3377346</v>
+        <v>7031896</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="E73" t="s">
-        <v>154</v>
+        <v>22</v>
+      </c>
+      <c r="G73" t="s">
+        <v>112</v>
       </c>
       <c r="H73" s="1"/>
+      <c r="J73" t="s">
+        <v>23</v>
+      </c>
       <c r="L73">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M73" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N73" s="2">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="O73" s="2">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="P73">
         <v>90</v>
@@ -4660,310 +4741,355 @@
         <v>20</v>
       </c>
       <c r="R73" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="S73" t="s">
         <v>20</v>
       </c>
       <c r="T73">
-        <v>7</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>344</v>
+        <v>236</v>
       </c>
       <c r="B74">
-        <v>4745432</v>
+        <v>7031896</v>
       </c>
       <c r="C74" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="E74" t="s">
-        <v>157</v>
+        <v>22</v>
+      </c>
+      <c r="G74" t="s">
+        <v>112</v>
       </c>
       <c r="H74" s="1"/>
+      <c r="J74" t="s">
+        <v>23</v>
+      </c>
       <c r="L74">
-        <v>1724163</v>
+        <v>1706681</v>
       </c>
       <c r="M74" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="N74" s="2">
-        <v>46238</v>
+        <v>46218</v>
       </c>
       <c r="O74" s="2">
-        <v>46238</v>
+        <v>46218</v>
       </c>
       <c r="P74">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="Q74" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R74" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="S74" t="s">
         <v>20</v>
       </c>
       <c r="T74">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>351</v>
+        <v>237</v>
       </c>
       <c r="B75">
-        <v>6232613</v>
+        <v>7031896</v>
       </c>
       <c r="C75" t="s">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="E75" t="s">
-        <v>160</v>
+        <v>22</v>
+      </c>
+      <c r="G75" t="s">
+        <v>112</v>
       </c>
       <c r="H75" s="1"/>
+      <c r="J75" t="s">
+        <v>23</v>
+      </c>
       <c r="L75">
-        <v>1724163</v>
+        <v>1711329</v>
       </c>
       <c r="M75" t="s">
-        <v>33</v>
+        <v>203</v>
       </c>
       <c r="N75" s="2">
-        <v>46238</v>
+        <v>46213</v>
       </c>
       <c r="O75" s="2">
-        <v>46238</v>
+        <v>46213</v>
       </c>
       <c r="P75">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q75" t="s">
         <v>20</v>
       </c>
       <c r="R75" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="S75" t="s">
         <v>20</v>
       </c>
       <c r="T75">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>357</v>
+        <v>240</v>
       </c>
       <c r="B76">
-        <v>5766619</v>
+        <v>7031895</v>
       </c>
       <c r="C76" t="s">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="D76" t="s">
-        <v>253</v>
+        <v>25</v>
+      </c>
+      <c r="E76" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" t="s">
+        <v>113</v>
       </c>
       <c r="H76" s="1"/>
+      <c r="J76" t="s">
+        <v>23</v>
+      </c>
       <c r="L76">
-        <v>1724163</v>
+        <v>1710979</v>
       </c>
       <c r="M76" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="N76" s="2">
-        <v>46244</v>
+        <v>46216</v>
       </c>
       <c r="O76" s="2">
-        <v>46244</v>
+        <v>46216</v>
       </c>
       <c r="P76">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q76" t="s">
         <v>20</v>
       </c>
       <c r="R76" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="S76" t="s">
         <v>20</v>
       </c>
       <c r="T76">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>360</v>
+        <v>241</v>
       </c>
       <c r="B77">
-        <v>7190758</v>
+        <v>7031895</v>
       </c>
       <c r="C77" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="E77" t="s">
-        <v>256</v>
+        <v>25</v>
+      </c>
+      <c r="G77" t="s">
+        <v>113</v>
       </c>
       <c r="H77" s="1"/>
+      <c r="J77" t="s">
+        <v>23</v>
+      </c>
       <c r="L77">
-        <v>1706681</v>
+        <v>1708464</v>
       </c>
       <c r="M77" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N77" s="2">
-        <v>46247</v>
+        <v>46211</v>
       </c>
       <c r="O77" s="2">
-        <v>46247</v>
+        <v>46211</v>
       </c>
       <c r="P77">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="Q77" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="R77" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="S77" t="s">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="T77">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>361</v>
+        <v>242</v>
       </c>
       <c r="B78">
-        <v>7190758</v>
+        <v>7031895</v>
       </c>
       <c r="C78" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="D78" t="s">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="E78" t="s">
-        <v>256</v>
+        <v>25</v>
+      </c>
+      <c r="G78" t="s">
+        <v>113</v>
       </c>
       <c r="H78" s="1"/>
+      <c r="J78" t="s">
+        <v>23</v>
+      </c>
       <c r="L78">
-        <v>1708464</v>
+        <v>1711329</v>
       </c>
       <c r="M78" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N78" s="2">
-        <v>46246</v>
+        <v>46213</v>
       </c>
       <c r="O78" s="2">
-        <v>46246</v>
+        <v>46213</v>
       </c>
       <c r="P78">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q78" t="s">
         <v>20</v>
       </c>
       <c r="R78" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="S78" t="s">
         <v>20</v>
       </c>
       <c r="T78">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>362</v>
+        <v>243</v>
       </c>
       <c r="B79">
-        <v>7190758</v>
+        <v>7031895</v>
       </c>
       <c r="C79" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="E79" t="s">
-        <v>256</v>
+        <v>25</v>
+      </c>
+      <c r="G79" t="s">
+        <v>113</v>
       </c>
       <c r="H79" s="1"/>
+      <c r="J79" t="s">
+        <v>23</v>
+      </c>
       <c r="L79">
-        <v>1723203</v>
+        <v>1724163</v>
       </c>
       <c r="M79" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N79" s="2">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="O79" s="2">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="P79">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q79" t="s">
         <v>20</v>
       </c>
       <c r="R79" t="s">
-        <v>259</v>
+        <v>42</v>
       </c>
       <c r="S79" t="s">
         <v>20</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="B80">
-        <v>7190758</v>
+        <v>7031895</v>
       </c>
       <c r="C80" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="D80" t="s">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="E80" t="s">
-        <v>256</v>
+        <v>25</v>
+      </c>
+      <c r="G80" t="s">
+        <v>113</v>
       </c>
       <c r="H80" s="1"/>
+      <c r="J80" t="s">
+        <v>23</v>
+      </c>
       <c r="L80">
-        <v>1706681</v>
+        <v>1715169</v>
       </c>
       <c r="M80" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="N80" s="2">
-        <v>46247</v>
+        <v>46218</v>
       </c>
       <c r="O80" s="2">
-        <v>46247</v>
+        <v>46218</v>
       </c>
       <c r="P80">
         <v>83</v>
@@ -4972,229 +5098,235 @@
         <v>20</v>
       </c>
       <c r="R80" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="S80" t="s">
         <v>20</v>
       </c>
       <c r="T80">
-        <v>29</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>364</v>
+        <v>245</v>
       </c>
       <c r="B81">
-        <v>7190758</v>
+        <v>7031895</v>
       </c>
       <c r="C81" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>256</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
-        <v>256</v>
+        <v>25</v>
+      </c>
+      <c r="G81" t="s">
+        <v>113</v>
       </c>
       <c r="H81" s="1"/>
+      <c r="J81" t="s">
+        <v>23</v>
+      </c>
       <c r="L81">
-        <v>1711329</v>
+        <v>1706681</v>
       </c>
       <c r="M81" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="N81" s="2">
-        <v>46246</v>
+        <v>46218</v>
       </c>
       <c r="O81" s="2">
-        <v>46246</v>
+        <v>46218</v>
       </c>
       <c r="P81">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="Q81" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R81" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="S81" t="s">
         <v>20</v>
       </c>
       <c r="T81">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>387</v>
+        <v>246</v>
       </c>
       <c r="B82">
-        <v>3377342</v>
+        <v>7031895</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>24</v>
       </c>
       <c r="D82" t="s">
-        <v>262</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
-        <v>262</v>
+        <v>25</v>
+      </c>
+      <c r="G82" t="s">
+        <v>113</v>
       </c>
       <c r="H82" s="1"/>
+      <c r="J82" t="s">
+        <v>23</v>
+      </c>
       <c r="L82">
-        <v>1724178</v>
+        <v>1706681</v>
       </c>
       <c r="M82" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="N82" s="2">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="O82" s="2">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="P82">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q82" t="s">
         <v>20</v>
       </c>
       <c r="R82" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="S82" t="s">
         <v>20</v>
       </c>
       <c r="T82">
-        <v>58</v>
+        <v>28480</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>388</v>
+        <v>255</v>
       </c>
       <c r="B83">
-        <v>3371025</v>
+        <v>6345154</v>
       </c>
       <c r="C83" t="s">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="E83" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="H83" s="1"/>
       <c r="L83">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M83" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N83" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="O83" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="P83">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q83" t="s">
         <v>20</v>
       </c>
       <c r="R83" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="S83" t="s">
         <v>20</v>
       </c>
       <c r="T83">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>389</v>
+        <v>257</v>
       </c>
       <c r="B84">
-        <v>3367776</v>
+        <v>6386085</v>
       </c>
       <c r="C84" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="D84" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="E84" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="H84" s="1"/>
       <c r="L84">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M84" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N84" s="2">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="O84" s="2">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="P84">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q84" t="s">
         <v>20</v>
       </c>
       <c r="R84" t="s">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="S84" t="s">
         <v>20</v>
       </c>
       <c r="T84">
-        <v>5498</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>394</v>
+        <v>258</v>
       </c>
       <c r="B85">
-        <v>7031897</v>
+        <v>3370070</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="D85" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="E85" t="s">
-        <v>27</v>
-      </c>
-      <c r="G85" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="H85" s="1"/>
-      <c r="J85" t="s">
-        <v>29</v>
-      </c>
       <c r="L85">
-        <v>1723203</v>
+        <v>1724178</v>
       </c>
       <c r="M85" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N85" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O85" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="P85">
         <v>100</v>
@@ -5203,7 +5335,7 @@
         <v>20</v>
       </c>
       <c r="R85" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="S85" t="s">
         <v>20</v>
@@ -5214,172 +5346,151 @@
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>396</v>
+        <v>259</v>
       </c>
       <c r="B86">
-        <v>7031897</v>
+        <v>3367914</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="D86" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="E86" t="s">
-        <v>27</v>
-      </c>
-      <c r="G86" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="H86" s="1"/>
-      <c r="J86" t="s">
-        <v>29</v>
-      </c>
       <c r="L86">
-        <v>1711329</v>
+        <v>1724163</v>
       </c>
       <c r="M86" t="s">
-        <v>223</v>
+        <v>33</v>
       </c>
       <c r="N86" s="2">
-        <v>46213</v>
+        <v>46241</v>
       </c>
       <c r="O86" s="2">
-        <v>46213</v>
+        <v>46241</v>
       </c>
       <c r="P86">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q86" t="s">
         <v>20</v>
       </c>
       <c r="R86" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="S86" t="s">
         <v>20</v>
       </c>
       <c r="T86">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>397</v>
+        <v>261</v>
       </c>
       <c r="B87">
-        <v>7031897</v>
+        <v>4745431</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
-      </c>
-      <c r="E87" t="s">
-        <v>27</v>
-      </c>
-      <c r="G87" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="H87" s="1"/>
-      <c r="J87" t="s">
-        <v>29</v>
-      </c>
       <c r="L87">
-        <v>1706681</v>
+        <v>1724163</v>
       </c>
       <c r="M87" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="N87" s="2">
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="O87" s="2">
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="P87">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="Q87" t="s">
         <v>20</v>
       </c>
       <c r="R87" t="s">
-        <v>265</v>
+        <v>125</v>
       </c>
       <c r="S87" t="s">
         <v>20</v>
       </c>
       <c r="T87">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>399</v>
+        <v>264</v>
       </c>
       <c r="B88">
-        <v>7031897</v>
+        <v>6222314</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="D88" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="E88" t="s">
-        <v>27</v>
-      </c>
-      <c r="G88" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="H88" s="1"/>
-      <c r="J88" t="s">
-        <v>29</v>
-      </c>
       <c r="L88">
-        <v>1708464</v>
+        <v>1723203</v>
       </c>
       <c r="M88" t="s">
-        <v>206</v>
+        <v>36</v>
       </c>
       <c r="N88" s="2">
-        <v>46211</v>
+        <v>46240</v>
       </c>
       <c r="O88" s="2">
-        <v>46211</v>
+        <v>46240</v>
       </c>
       <c r="P88">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Q88" t="s">
         <v>20</v>
       </c>
       <c r="R88" t="s">
-        <v>266</v>
+        <v>128</v>
       </c>
       <c r="S88" t="s">
         <v>20</v>
       </c>
       <c r="T88">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>405</v>
+        <v>265</v>
       </c>
       <c r="B89">
-        <v>3371114</v>
+        <v>3394648</v>
       </c>
       <c r="C89" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="D89" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="E89" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="H89" s="1"/>
       <c r="L89">
@@ -5389,87 +5500,90 @@
         <v>40</v>
       </c>
       <c r="N89" s="2">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="O89" s="2">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="P89">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Q89" t="s">
         <v>20</v>
       </c>
       <c r="R89" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="S89" t="s">
         <v>20</v>
       </c>
       <c r="T89">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>408</v>
+        <v>267</v>
       </c>
       <c r="B90">
-        <v>3372145</v>
+        <v>3797743</v>
       </c>
       <c r="C90" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="E90" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="H90" s="1"/>
+      <c r="K90" t="s">
+        <v>134</v>
+      </c>
       <c r="L90">
-        <v>1724178</v>
+        <v>1724163</v>
       </c>
       <c r="M90" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N90" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="O90" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="P90">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q90" t="s">
         <v>20</v>
       </c>
       <c r="R90" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="S90" t="s">
         <v>20</v>
       </c>
       <c r="T90">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>409</v>
+        <v>274</v>
       </c>
       <c r="B91">
-        <v>3562642</v>
+        <v>7318791</v>
       </c>
       <c r="C91" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D91" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E91" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H91" s="1"/>
       <c r="L91">
@@ -5479,55 +5593,55 @@
         <v>33</v>
       </c>
       <c r="N91" s="2">
-        <v>46245</v>
+        <v>46282</v>
       </c>
       <c r="O91" s="2">
-        <v>46245</v>
+        <v>46282</v>
       </c>
       <c r="P91">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="Q91" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R91" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="S91" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T91">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>414</v>
+        <v>277</v>
       </c>
       <c r="B92">
-        <v>6546621</v>
+        <v>6429181</v>
       </c>
       <c r="C92" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D92" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E92" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H92" s="1"/>
       <c r="L92">
-        <v>1708579</v>
+        <v>1724163</v>
       </c>
       <c r="M92" t="s">
-        <v>272</v>
+        <v>33</v>
       </c>
       <c r="N92" s="2">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="O92" s="2">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="P92">
         <v>90</v>
@@ -5536,88 +5650,88 @@
         <v>20</v>
       </c>
       <c r="R92" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="S92" t="s">
         <v>20</v>
       </c>
       <c r="T92">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>415</v>
+        <v>279</v>
       </c>
       <c r="B93">
-        <v>6546621</v>
+        <v>7318790</v>
       </c>
       <c r="C93" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="E93" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="H93" s="1"/>
       <c r="L93">
-        <v>1708695</v>
+        <v>1724163</v>
       </c>
       <c r="M93" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
       <c r="N93" s="2">
-        <v>46223</v>
+        <v>46282</v>
       </c>
       <c r="O93" s="2">
-        <v>46223</v>
+        <v>46282</v>
       </c>
       <c r="P93">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q93" t="s">
         <v>20</v>
       </c>
       <c r="R93" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="S93" t="s">
         <v>20</v>
       </c>
       <c r="T93">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>416</v>
+        <v>302</v>
       </c>
       <c r="B94">
-        <v>6546621</v>
+        <v>3406205</v>
       </c>
       <c r="C94" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="D94" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="E94" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="H94" s="1"/>
       <c r="L94">
-        <v>1708464</v>
+        <v>1723203</v>
       </c>
       <c r="M94" t="s">
-        <v>206</v>
+        <v>36</v>
       </c>
       <c r="N94" s="2">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="O94" s="2">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="P94">
         <v>100</v>
@@ -5626,75 +5740,75 @@
         <v>20</v>
       </c>
       <c r="R94" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="S94" t="s">
         <v>20</v>
       </c>
       <c r="T94">
-        <v>18</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>417</v>
+        <v>303</v>
       </c>
       <c r="B95">
-        <v>6546621</v>
+        <v>3406205</v>
       </c>
       <c r="C95" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="D95" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="E95" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="H95" s="1"/>
       <c r="L95">
-        <v>1706681</v>
+        <v>1724178</v>
       </c>
       <c r="M95" t="s">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="N95" s="2">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="O95" s="2">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="P95">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="Q95" t="s">
         <v>20</v>
       </c>
       <c r="R95" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="S95" t="s">
         <v>20</v>
       </c>
       <c r="T95">
-        <v>10</v>
+        <v>7259</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>420</v>
+        <v>304</v>
       </c>
       <c r="B96">
-        <v>6386084</v>
+        <v>3406205</v>
       </c>
       <c r="C96" t="s">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="D96" t="s">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="E96" t="s">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="H96" s="1"/>
       <c r="L96">
@@ -5704,100 +5818,100 @@
         <v>33</v>
       </c>
       <c r="N96" s="2">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="O96" s="2">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="P96">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q96" t="s">
         <v>20</v>
       </c>
       <c r="R96" t="s">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="S96" t="s">
         <v>20</v>
       </c>
       <c r="T96">
-        <v>3</v>
+        <v>7271</v>
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>422</v>
+        <v>305</v>
       </c>
       <c r="B97">
-        <v>7135138</v>
+        <v>3406205</v>
       </c>
       <c r="C97" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="D97" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="E97" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="H97" s="1"/>
       <c r="L97">
-        <v>1711329</v>
+        <v>1715169</v>
       </c>
       <c r="M97" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="N97" s="2">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="O97" s="2">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="P97">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="Q97" t="s">
         <v>20</v>
       </c>
       <c r="R97" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S97" t="s">
         <v>20</v>
       </c>
       <c r="T97">
-        <v>6</v>
+        <v>63386</v>
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>423</v>
+        <v>306</v>
       </c>
       <c r="B98">
-        <v>7135138</v>
+        <v>3406205</v>
       </c>
       <c r="C98" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="D98" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="E98" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="H98" s="1"/>
       <c r="L98">
-        <v>1708464</v>
+        <v>1711329</v>
       </c>
       <c r="M98" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N98" s="2">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="O98" s="2">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="P98">
         <v>100</v>
@@ -5806,88 +5920,88 @@
         <v>20</v>
       </c>
       <c r="R98" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S98" t="s">
         <v>20</v>
       </c>
       <c r="T98">
-        <v>2830</v>
+        <v>63407</v>
       </c>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>424</v>
+        <v>307</v>
       </c>
       <c r="B99">
-        <v>7135138</v>
+        <v>3406205</v>
       </c>
       <c r="C99" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="D99" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="E99" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="H99" s="1"/>
       <c r="L99">
-        <v>1708715</v>
+        <v>1706681</v>
       </c>
       <c r="M99" t="s">
-        <v>285</v>
+        <v>170</v>
       </c>
       <c r="N99" s="2">
-        <v>46240</v>
+        <v>46218</v>
       </c>
       <c r="O99" s="2">
-        <v>46240</v>
+        <v>46218</v>
       </c>
       <c r="P99">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q99" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R99" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="S99" t="s">
         <v>20</v>
       </c>
       <c r="T99">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>425</v>
+        <v>308</v>
       </c>
       <c r="B100">
-        <v>7135138</v>
+        <v>3406205</v>
       </c>
       <c r="C100" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="D100" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="E100" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="H100" s="1"/>
       <c r="L100">
-        <v>1708474</v>
+        <v>1708464</v>
       </c>
       <c r="M100" t="s">
-        <v>287</v>
+        <v>194</v>
       </c>
       <c r="N100" s="2">
-        <v>46242</v>
+        <v>46206</v>
       </c>
       <c r="O100" s="2">
-        <v>46242</v>
+        <v>46206</v>
       </c>
       <c r="P100">
         <v>100</v>
@@ -5896,7 +6010,7 @@
         <v>20</v>
       </c>
       <c r="R100" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="S100" t="s">
         <v>20</v>
@@ -5907,77 +6021,77 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>426</v>
+        <v>309</v>
       </c>
       <c r="B101">
-        <v>7135138</v>
+        <v>3406205</v>
       </c>
       <c r="C101" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="D101" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="E101" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="H101" s="1"/>
       <c r="L101">
-        <v>1706681</v>
+        <v>1710979</v>
       </c>
       <c r="M101" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="N101" s="2">
-        <v>46240</v>
+        <v>46261</v>
       </c>
       <c r="O101" s="2">
-        <v>46240</v>
+        <v>46261</v>
       </c>
       <c r="P101">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="Q101" t="s">
         <v>20</v>
       </c>
       <c r="R101" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="S101" t="s">
         <v>20</v>
       </c>
       <c r="T101">
-        <v>12</v>
+        <v>63471</v>
       </c>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>429</v>
+        <v>310</v>
       </c>
       <c r="B102">
-        <v>7135138</v>
+        <v>3406205</v>
       </c>
       <c r="C102" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="E102" t="s">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="H102" s="1"/>
       <c r="L102">
-        <v>1708579</v>
+        <v>1706681</v>
       </c>
       <c r="M102" t="s">
-        <v>272</v>
+        <v>170</v>
       </c>
       <c r="N102" s="2">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="O102" s="2">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="P102">
         <v>100</v>
@@ -5986,85 +6100,88 @@
         <v>20</v>
       </c>
       <c r="R102" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="S102" t="s">
         <v>20</v>
       </c>
       <c r="T102">
-        <v>2</v>
+        <v>61495</v>
       </c>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>431</v>
+        <v>311</v>
       </c>
       <c r="B103">
-        <v>7135138</v>
+        <v>3384439</v>
       </c>
       <c r="C103" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D103" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E103" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="H103" s="1"/>
       <c r="L103">
-        <v>1708695</v>
+        <v>1724178</v>
       </c>
       <c r="M103" t="s">
-        <v>274</v>
+        <v>40</v>
       </c>
       <c r="N103" s="2">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="O103" s="2">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="P103">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="Q103" t="s">
         <v>20</v>
       </c>
       <c r="R103" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S103" t="s">
         <v>20</v>
       </c>
       <c r="T103">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>432</v>
+        <v>312</v>
       </c>
       <c r="B104">
-        <v>5005208</v>
+        <v>3379507</v>
       </c>
       <c r="C104" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D104" t="s">
-        <v>175</v>
+        <v>142</v>
+      </c>
+      <c r="E104" t="s">
+        <v>142</v>
       </c>
       <c r="H104" s="1"/>
       <c r="L104">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M104" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N104" s="2">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="O104" s="2">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="P104">
         <v>100</v>
@@ -6073,88 +6190,88 @@
         <v>20</v>
       </c>
       <c r="R104" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="S104" t="s">
         <v>20</v>
       </c>
       <c r="T104">
-        <v>1399</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>435</v>
+        <v>313</v>
       </c>
       <c r="B105">
-        <v>6484813</v>
+        <v>3373183</v>
       </c>
       <c r="C105" t="s">
-        <v>177</v>
+        <v>291</v>
       </c>
       <c r="D105" t="s">
-        <v>178</v>
+        <v>292</v>
       </c>
       <c r="E105" t="s">
-        <v>178</v>
+        <v>292</v>
       </c>
       <c r="H105" s="1"/>
       <c r="L105">
-        <v>1724163</v>
+        <v>1724178</v>
       </c>
       <c r="M105" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N105" s="2">
-        <v>46238</v>
+        <v>46303</v>
       </c>
       <c r="O105" s="2">
-        <v>46238</v>
+        <v>46303</v>
       </c>
       <c r="P105">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q105" t="s">
         <v>20</v>
       </c>
       <c r="R105" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="S105" t="s">
         <v>20</v>
       </c>
       <c r="T105">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="B106">
-        <v>5816942</v>
+        <v>3369242</v>
       </c>
       <c r="C106" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="D106" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="E106" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="H106" s="1"/>
       <c r="L106">
-        <v>1723203</v>
+        <v>1724163</v>
       </c>
       <c r="M106" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N106" s="2">
-        <v>46232</v>
+        <v>46243</v>
       </c>
       <c r="O106" s="2">
-        <v>46232</v>
+        <v>46243</v>
       </c>
       <c r="P106">
         <v>100</v>
@@ -6163,7 +6280,7 @@
         <v>20</v>
       </c>
       <c r="R106" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="S106" t="s">
         <v>20</v>
@@ -6174,535 +6291,2020 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>444</v>
+        <v>371</v>
       </c>
       <c r="B107">
-        <v>5816942</v>
+        <v>6921313</v>
       </c>
       <c r="C107" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="E107" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="H107" s="1"/>
       <c r="L107">
         <v>1706681</v>
       </c>
       <c r="M107" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="N107" s="2">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="O107" s="2">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="P107">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="Q107" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R107" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S107" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T107">
-        <v>151</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="B108">
-        <v>5816942</v>
+        <v>6921313</v>
       </c>
       <c r="C108" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="E108" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="H108" s="1"/>
       <c r="L108">
-        <v>1724163</v>
+        <v>1711378</v>
       </c>
       <c r="M108" t="s">
-        <v>33</v>
+        <v>295</v>
       </c>
       <c r="N108" s="2">
-        <v>46232</v>
+        <v>46273</v>
       </c>
       <c r="O108" s="2">
-        <v>46232</v>
+        <v>46273</v>
       </c>
       <c r="P108">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="Q108" t="s">
         <v>20</v>
       </c>
       <c r="R108" t="s">
-        <v>183</v>
+        <v>296</v>
       </c>
       <c r="S108" t="s">
         <v>20</v>
       </c>
       <c r="T108">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>450</v>
+        <v>373</v>
       </c>
       <c r="B109">
-        <v>4266142</v>
+        <v>6921313</v>
       </c>
       <c r="C109" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="D109" t="s">
-        <v>293</v>
+        <v>148</v>
+      </c>
+      <c r="E109" t="s">
+        <v>148</v>
       </c>
       <c r="H109" s="1"/>
       <c r="L109">
-        <v>1724163</v>
+        <v>1715169</v>
       </c>
       <c r="M109" t="s">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="N109" s="2">
-        <v>46245</v>
+        <v>46273</v>
       </c>
       <c r="O109" s="2">
-        <v>46245</v>
+        <v>46273</v>
       </c>
       <c r="P109">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q109" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R109" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="S109" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T109">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>459</v>
+        <v>374</v>
       </c>
       <c r="B110">
-        <v>5863016</v>
+        <v>6921313</v>
       </c>
       <c r="C110" t="s">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="D110" t="s">
-        <v>295</v>
+        <v>148</v>
+      </c>
+      <c r="E110" t="s">
+        <v>148</v>
       </c>
       <c r="H110" s="1"/>
       <c r="L110">
-        <v>1723203</v>
+        <v>1724163</v>
       </c>
       <c r="M110" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N110" s="2">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="O110" s="2">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="P110">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q110" t="s">
         <v>20</v>
       </c>
       <c r="R110" t="s">
-        <v>296</v>
+        <v>149</v>
       </c>
       <c r="S110" t="s">
         <v>20</v>
       </c>
       <c r="T110">
-        <v>9025</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>460</v>
+        <v>375</v>
       </c>
       <c r="B111">
-        <v>4264886</v>
+        <v>6921313</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="D111" t="s">
-        <v>184</v>
+        <v>148</v>
+      </c>
+      <c r="E111" t="s">
+        <v>148</v>
       </c>
       <c r="H111" s="1"/>
       <c r="L111">
-        <v>1724163</v>
+        <v>1706681</v>
       </c>
       <c r="M111" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="N111" s="2">
-        <v>46240</v>
+        <v>46273</v>
       </c>
       <c r="O111" s="2">
-        <v>46240</v>
+        <v>46273</v>
       </c>
       <c r="P111">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="Q111" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R111" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="S111" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T111">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>469</v>
+        <v>376</v>
       </c>
       <c r="B112">
-        <v>4264864</v>
+        <v>6921313</v>
       </c>
       <c r="C112" t="s">
-        <v>297</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
-        <v>297</v>
+        <v>148</v>
+      </c>
+      <c r="E112" t="s">
+        <v>148</v>
       </c>
       <c r="H112" s="1"/>
       <c r="L112">
-        <v>1724163</v>
+        <v>1715169</v>
       </c>
       <c r="M112" t="s">
-        <v>33</v>
+        <v>259</v>
       </c>
       <c r="N112" s="2">
-        <v>46245</v>
+        <v>46273</v>
       </c>
       <c r="O112" s="2">
-        <v>46245</v>
+        <v>46273</v>
       </c>
       <c r="P112">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="Q112" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="R112" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S112" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="T112">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>471</v>
+        <v>377</v>
       </c>
       <c r="B113">
-        <v>5360489</v>
+        <v>6921313</v>
       </c>
       <c r="C113" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="D113" t="s">
-        <v>186</v>
+        <v>148</v>
+      </c>
+      <c r="E113" t="s">
+        <v>148</v>
       </c>
       <c r="H113" s="1"/>
       <c r="L113">
+        <v>1710979</v>
+      </c>
+      <c r="M113" t="s">
+        <v>201</v>
+      </c>
+      <c r="N113" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O113" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P113">
+        <v>83</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>20</v>
+      </c>
+      <c r="R113" t="s">
+        <v>298</v>
+      </c>
+      <c r="S113" t="s">
+        <v>20</v>
+      </c>
+      <c r="T113">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>378</v>
+      </c>
+      <c r="B114">
+        <v>6921313</v>
+      </c>
+      <c r="C114" t="s">
+        <v>147</v>
+      </c>
+      <c r="D114" t="s">
+        <v>148</v>
+      </c>
+      <c r="E114" t="s">
+        <v>148</v>
+      </c>
+      <c r="H114" s="1"/>
+      <c r="L114">
+        <v>1706681</v>
+      </c>
+      <c r="M114" t="s">
+        <v>170</v>
+      </c>
+      <c r="N114" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O114" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P114">
+        <v>67</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>198</v>
+      </c>
+      <c r="R114" t="s">
+        <v>294</v>
+      </c>
+      <c r="S114" t="s">
+        <v>198</v>
+      </c>
+      <c r="T114">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>379</v>
+      </c>
+      <c r="B115">
+        <v>6921313</v>
+      </c>
+      <c r="C115" t="s">
+        <v>147</v>
+      </c>
+      <c r="D115" t="s">
+        <v>148</v>
+      </c>
+      <c r="E115" t="s">
+        <v>148</v>
+      </c>
+      <c r="H115" s="1"/>
+      <c r="L115">
+        <v>1715169</v>
+      </c>
+      <c r="M115" t="s">
+        <v>259</v>
+      </c>
+      <c r="N115" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O115" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P115">
+        <v>75</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>20</v>
+      </c>
+      <c r="R115" t="s">
+        <v>297</v>
+      </c>
+      <c r="S115" t="s">
+        <v>20</v>
+      </c>
+      <c r="T115">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>380</v>
+      </c>
+      <c r="B116">
+        <v>6921313</v>
+      </c>
+      <c r="C116" t="s">
+        <v>147</v>
+      </c>
+      <c r="D116" t="s">
+        <v>148</v>
+      </c>
+      <c r="E116" t="s">
+        <v>148</v>
+      </c>
+      <c r="H116" s="1"/>
+      <c r="L116">
+        <v>1708464</v>
+      </c>
+      <c r="M116" t="s">
+        <v>194</v>
+      </c>
+      <c r="N116" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O116" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P116">
+        <v>80</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>20</v>
+      </c>
+      <c r="R116" t="s">
+        <v>299</v>
+      </c>
+      <c r="S116" t="s">
+        <v>20</v>
+      </c>
+      <c r="T116">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>381</v>
+      </c>
+      <c r="B117">
+        <v>6921313</v>
+      </c>
+      <c r="C117" t="s">
+        <v>147</v>
+      </c>
+      <c r="D117" t="s">
+        <v>148</v>
+      </c>
+      <c r="E117" t="s">
+        <v>148</v>
+      </c>
+      <c r="H117" s="1"/>
+      <c r="L117">
+        <v>1711329</v>
+      </c>
+      <c r="M117" t="s">
+        <v>203</v>
+      </c>
+      <c r="N117" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O117" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P117">
+        <v>100</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>20</v>
+      </c>
+      <c r="R117" t="s">
+        <v>300</v>
+      </c>
+      <c r="S117" t="s">
+        <v>20</v>
+      </c>
+      <c r="T117">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>382</v>
+      </c>
+      <c r="B118">
+        <v>6921313</v>
+      </c>
+      <c r="C118" t="s">
+        <v>147</v>
+      </c>
+      <c r="D118" t="s">
+        <v>148</v>
+      </c>
+      <c r="E118" t="s">
+        <v>148</v>
+      </c>
+      <c r="H118" s="1"/>
+      <c r="L118">
+        <v>1706681</v>
+      </c>
+      <c r="M118" t="s">
+        <v>170</v>
+      </c>
+      <c r="N118" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O118" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P118">
+        <v>58</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>20</v>
+      </c>
+      <c r="R118" t="s">
+        <v>294</v>
+      </c>
+      <c r="S118" t="s">
+        <v>20</v>
+      </c>
+      <c r="T118">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>383</v>
+      </c>
+      <c r="B119">
+        <v>6921313</v>
+      </c>
+      <c r="C119" t="s">
+        <v>147</v>
+      </c>
+      <c r="D119" t="s">
+        <v>148</v>
+      </c>
+      <c r="E119" t="s">
+        <v>148</v>
+      </c>
+      <c r="H119" s="1"/>
+      <c r="L119">
+        <v>1710979</v>
+      </c>
+      <c r="M119" t="s">
+        <v>201</v>
+      </c>
+      <c r="N119" s="2">
+        <v>46273</v>
+      </c>
+      <c r="O119" s="2">
+        <v>46273</v>
+      </c>
+      <c r="P119">
+        <v>67</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>198</v>
+      </c>
+      <c r="R119" t="s">
+        <v>298</v>
+      </c>
+      <c r="S119" t="s">
+        <v>198</v>
+      </c>
+      <c r="T119">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>389</v>
+      </c>
+      <c r="B120">
+        <v>3377340</v>
+      </c>
+      <c r="C120" t="s">
+        <v>301</v>
+      </c>
+      <c r="D120" t="s">
+        <v>302</v>
+      </c>
+      <c r="E120" t="s">
+        <v>302</v>
+      </c>
+      <c r="H120" s="1"/>
+      <c r="L120">
         <v>1724178</v>
       </c>
-      <c r="M113" t="s">
+      <c r="M120" t="s">
         <v>40</v>
       </c>
-      <c r="N113" s="2">
+      <c r="N120" s="2">
+        <v>46245</v>
+      </c>
+      <c r="O120" s="2">
+        <v>46245</v>
+      </c>
+      <c r="P120">
+        <v>100</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>20</v>
+      </c>
+      <c r="R120" t="s">
+        <v>303</v>
+      </c>
+      <c r="S120" t="s">
+        <v>20</v>
+      </c>
+      <c r="T120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>390</v>
+      </c>
+      <c r="B121">
+        <v>3419303</v>
+      </c>
+      <c r="C121" t="s">
+        <v>304</v>
+      </c>
+      <c r="D121" t="s">
+        <v>305</v>
+      </c>
+      <c r="E121" t="s">
+        <v>305</v>
+      </c>
+      <c r="H121" s="1"/>
+      <c r="L121">
+        <v>1724163</v>
+      </c>
+      <c r="M121" t="s">
+        <v>33</v>
+      </c>
+      <c r="N121" s="2">
+        <v>46244</v>
+      </c>
+      <c r="O121" s="2">
+        <v>46244</v>
+      </c>
+      <c r="P121">
+        <v>100</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>20</v>
+      </c>
+      <c r="R121" t="s">
+        <v>306</v>
+      </c>
+      <c r="S121" t="s">
+        <v>20</v>
+      </c>
+      <c r="T121">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>391</v>
+      </c>
+      <c r="B122">
+        <v>3377339</v>
+      </c>
+      <c r="C122" t="s">
+        <v>150</v>
+      </c>
+      <c r="D122" t="s">
+        <v>151</v>
+      </c>
+      <c r="E122" t="s">
+        <v>151</v>
+      </c>
+      <c r="H122" s="1"/>
+      <c r="L122">
+        <v>1724178</v>
+      </c>
+      <c r="M122" t="s">
+        <v>40</v>
+      </c>
+      <c r="N122" s="2">
+        <v>46241</v>
+      </c>
+      <c r="O122" s="2">
+        <v>46241</v>
+      </c>
+      <c r="P122">
+        <v>100</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>20</v>
+      </c>
+      <c r="R122" t="s">
+        <v>152</v>
+      </c>
+      <c r="S122" t="s">
+        <v>20</v>
+      </c>
+      <c r="T122">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>401</v>
+      </c>
+      <c r="B123">
+        <v>3377346</v>
+      </c>
+      <c r="C123" t="s">
+        <v>153</v>
+      </c>
+      <c r="D123" t="s">
+        <v>154</v>
+      </c>
+      <c r="E123" t="s">
+        <v>154</v>
+      </c>
+      <c r="H123" s="1"/>
+      <c r="L123">
+        <v>1724178</v>
+      </c>
+      <c r="M123" t="s">
+        <v>40</v>
+      </c>
+      <c r="N123" s="2">
+        <v>46244</v>
+      </c>
+      <c r="O123" s="2">
+        <v>46244</v>
+      </c>
+      <c r="P123">
+        <v>90</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>20</v>
+      </c>
+      <c r="R123" t="s">
+        <v>155</v>
+      </c>
+      <c r="S123" t="s">
+        <v>20</v>
+      </c>
+      <c r="T123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>426</v>
+      </c>
+      <c r="B124">
+        <v>4745432</v>
+      </c>
+      <c r="C124" t="s">
+        <v>156</v>
+      </c>
+      <c r="D124" t="s">
+        <v>157</v>
+      </c>
+      <c r="E124" t="s">
+        <v>157</v>
+      </c>
+      <c r="H124" s="1"/>
+      <c r="L124">
+        <v>1724163</v>
+      </c>
+      <c r="M124" t="s">
+        <v>33</v>
+      </c>
+      <c r="N124" s="2">
+        <v>46238</v>
+      </c>
+      <c r="O124" s="2">
+        <v>46238</v>
+      </c>
+      <c r="P124">
+        <v>90</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>20</v>
+      </c>
+      <c r="R124" t="s">
+        <v>158</v>
+      </c>
+      <c r="S124" t="s">
+        <v>20</v>
+      </c>
+      <c r="T124">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>429</v>
+      </c>
+      <c r="B125">
+        <v>5267185</v>
+      </c>
+      <c r="C125" t="s">
+        <v>307</v>
+      </c>
+      <c r="D125" t="s">
+        <v>308</v>
+      </c>
+      <c r="H125" s="1"/>
+      <c r="L125">
+        <v>1724163</v>
+      </c>
+      <c r="M125" t="s">
+        <v>33</v>
+      </c>
+      <c r="N125" s="2">
+        <v>46279</v>
+      </c>
+      <c r="O125" s="2">
+        <v>46279</v>
+      </c>
+      <c r="P125">
+        <v>100</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>20</v>
+      </c>
+      <c r="R125" t="s">
+        <v>309</v>
+      </c>
+      <c r="S125" t="s">
+        <v>20</v>
+      </c>
+      <c r="T125">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>430</v>
+      </c>
+      <c r="B126">
+        <v>5267185</v>
+      </c>
+      <c r="C126" t="s">
+        <v>307</v>
+      </c>
+      <c r="D126" t="s">
+        <v>308</v>
+      </c>
+      <c r="H126" s="1"/>
+      <c r="L126">
+        <v>1724178</v>
+      </c>
+      <c r="M126" t="s">
+        <v>40</v>
+      </c>
+      <c r="N126" s="2">
+        <v>46279</v>
+      </c>
+      <c r="O126" s="2">
+        <v>46279</v>
+      </c>
+      <c r="P126">
+        <v>70</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>20</v>
+      </c>
+      <c r="R126" t="s">
+        <v>310</v>
+      </c>
+      <c r="S126" t="s">
+        <v>20</v>
+      </c>
+      <c r="T126">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>431</v>
+      </c>
+      <c r="B127">
+        <v>5267185</v>
+      </c>
+      <c r="C127" t="s">
+        <v>307</v>
+      </c>
+      <c r="D127" t="s">
+        <v>308</v>
+      </c>
+      <c r="H127" s="1"/>
+      <c r="L127">
+        <v>1723203</v>
+      </c>
+      <c r="M127" t="s">
+        <v>36</v>
+      </c>
+      <c r="N127" s="2">
+        <v>46279</v>
+      </c>
+      <c r="O127" s="2">
+        <v>46279</v>
+      </c>
+      <c r="P127">
+        <v>100</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>20</v>
+      </c>
+      <c r="R127" t="s">
+        <v>311</v>
+      </c>
+      <c r="S127" t="s">
+        <v>20</v>
+      </c>
+      <c r="T127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>437</v>
+      </c>
+      <c r="B128">
+        <v>6232613</v>
+      </c>
+      <c r="C128" t="s">
+        <v>159</v>
+      </c>
+      <c r="D128" t="s">
+        <v>160</v>
+      </c>
+      <c r="E128" t="s">
+        <v>160</v>
+      </c>
+      <c r="H128" s="1"/>
+      <c r="L128">
+        <v>1724163</v>
+      </c>
+      <c r="M128" t="s">
+        <v>33</v>
+      </c>
+      <c r="N128" s="2">
+        <v>46238</v>
+      </c>
+      <c r="O128" s="2">
+        <v>46238</v>
+      </c>
+      <c r="P128">
+        <v>100</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>20</v>
+      </c>
+      <c r="R128" t="s">
+        <v>161</v>
+      </c>
+      <c r="S128" t="s">
+        <v>20</v>
+      </c>
+      <c r="T128">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>444</v>
+      </c>
+      <c r="B129">
+        <v>5766619</v>
+      </c>
+      <c r="C129" t="s">
+        <v>312</v>
+      </c>
+      <c r="D129" t="s">
+        <v>313</v>
+      </c>
+      <c r="H129" s="1"/>
+      <c r="L129">
+        <v>1724163</v>
+      </c>
+      <c r="M129" t="s">
+        <v>33</v>
+      </c>
+      <c r="N129" s="2">
+        <v>46244</v>
+      </c>
+      <c r="O129" s="2">
+        <v>46244</v>
+      </c>
+      <c r="P129">
+        <v>90</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>20</v>
+      </c>
+      <c r="R129" t="s">
+        <v>314</v>
+      </c>
+      <c r="S129" t="s">
+        <v>20</v>
+      </c>
+      <c r="T129">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>446</v>
+      </c>
+      <c r="B130">
+        <v>7190758</v>
+      </c>
+      <c r="C130" t="s">
+        <v>315</v>
+      </c>
+      <c r="D130" t="s">
+        <v>316</v>
+      </c>
+      <c r="E130" t="s">
+        <v>316</v>
+      </c>
+      <c r="H130" s="1"/>
+      <c r="L130">
+        <v>1711329</v>
+      </c>
+      <c r="M130" t="s">
+        <v>203</v>
+      </c>
+      <c r="N130" s="2">
+        <v>46246</v>
+      </c>
+      <c r="O130" s="2">
+        <v>46246</v>
+      </c>
+      <c r="P130">
+        <v>90</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>20</v>
+      </c>
+      <c r="R130" t="s">
+        <v>317</v>
+      </c>
+      <c r="S130" t="s">
+        <v>20</v>
+      </c>
+      <c r="T130">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>447</v>
+      </c>
+      <c r="B131">
+        <v>7190758</v>
+      </c>
+      <c r="C131" t="s">
+        <v>315</v>
+      </c>
+      <c r="D131" t="s">
+        <v>316</v>
+      </c>
+      <c r="E131" t="s">
+        <v>316</v>
+      </c>
+      <c r="H131" s="1"/>
+      <c r="L131">
+        <v>1710979</v>
+      </c>
+      <c r="M131" t="s">
+        <v>201</v>
+      </c>
+      <c r="N131" s="2">
+        <v>46245</v>
+      </c>
+      <c r="O131" s="2">
+        <v>46245</v>
+      </c>
+      <c r="P131">
+        <v>75</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>20</v>
+      </c>
+      <c r="R131" t="s">
+        <v>318</v>
+      </c>
+      <c r="S131" t="s">
+        <v>20</v>
+      </c>
+      <c r="T131">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>448</v>
+      </c>
+      <c r="B132">
+        <v>7190758</v>
+      </c>
+      <c r="C132" t="s">
+        <v>315</v>
+      </c>
+      <c r="D132" t="s">
+        <v>316</v>
+      </c>
+      <c r="E132" t="s">
+        <v>316</v>
+      </c>
+      <c r="H132" s="1"/>
+      <c r="L132">
+        <v>1706681</v>
+      </c>
+      <c r="M132" t="s">
+        <v>170</v>
+      </c>
+      <c r="N132" s="2">
+        <v>46247</v>
+      </c>
+      <c r="O132" s="2">
+        <v>46247</v>
+      </c>
+      <c r="P132">
+        <v>67</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>198</v>
+      </c>
+      <c r="R132" t="s">
+        <v>319</v>
+      </c>
+      <c r="S132" t="s">
+        <v>198</v>
+      </c>
+      <c r="T132">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>449</v>
+      </c>
+      <c r="B133">
+        <v>7190758</v>
+      </c>
+      <c r="C133" t="s">
+        <v>315</v>
+      </c>
+      <c r="D133" t="s">
+        <v>316</v>
+      </c>
+      <c r="E133" t="s">
+        <v>316</v>
+      </c>
+      <c r="H133" s="1"/>
+      <c r="L133">
+        <v>1706681</v>
+      </c>
+      <c r="M133" t="s">
+        <v>170</v>
+      </c>
+      <c r="N133" s="2">
+        <v>46247</v>
+      </c>
+      <c r="O133" s="2">
+        <v>46247</v>
+      </c>
+      <c r="P133">
+        <v>83</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>20</v>
+      </c>
+      <c r="R133" t="s">
+        <v>319</v>
+      </c>
+      <c r="S133" t="s">
+        <v>20</v>
+      </c>
+      <c r="T133">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>450</v>
+      </c>
+      <c r="B134">
+        <v>7190758</v>
+      </c>
+      <c r="C134" t="s">
+        <v>315</v>
+      </c>
+      <c r="D134" t="s">
+        <v>316</v>
+      </c>
+      <c r="E134" t="s">
+        <v>316</v>
+      </c>
+      <c r="H134" s="1"/>
+      <c r="L134">
+        <v>1723203</v>
+      </c>
+      <c r="M134" t="s">
+        <v>36</v>
+      </c>
+      <c r="N134" s="2">
+        <v>46246</v>
+      </c>
+      <c r="O134" s="2">
+        <v>46246</v>
+      </c>
+      <c r="P134">
+        <v>100</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>20</v>
+      </c>
+      <c r="R134" t="s">
+        <v>320</v>
+      </c>
+      <c r="S134" t="s">
+        <v>20</v>
+      </c>
+      <c r="T134">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>451</v>
+      </c>
+      <c r="B135">
+        <v>7190758</v>
+      </c>
+      <c r="C135" t="s">
+        <v>315</v>
+      </c>
+      <c r="D135" t="s">
+        <v>316</v>
+      </c>
+      <c r="E135" t="s">
+        <v>316</v>
+      </c>
+      <c r="H135" s="1"/>
+      <c r="L135">
+        <v>1708464</v>
+      </c>
+      <c r="M135" t="s">
+        <v>194</v>
+      </c>
+      <c r="N135" s="2">
+        <v>46246</v>
+      </c>
+      <c r="O135" s="2">
+        <v>46246</v>
+      </c>
+      <c r="P135">
+        <v>90</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>20</v>
+      </c>
+      <c r="R135" t="s">
+        <v>321</v>
+      </c>
+      <c r="S135" t="s">
+        <v>20</v>
+      </c>
+      <c r="T135">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>474</v>
+      </c>
+      <c r="B136">
+        <v>3377342</v>
+      </c>
+      <c r="C136" t="s">
+        <v>322</v>
+      </c>
+      <c r="D136" t="s">
+        <v>323</v>
+      </c>
+      <c r="E136" t="s">
+        <v>323</v>
+      </c>
+      <c r="H136" s="1"/>
+      <c r="L136">
+        <v>1724178</v>
+      </c>
+      <c r="M136" t="s">
+        <v>40</v>
+      </c>
+      <c r="N136" s="2">
+        <v>46245</v>
+      </c>
+      <c r="O136" s="2">
+        <v>46245</v>
+      </c>
+      <c r="P136">
+        <v>80</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>20</v>
+      </c>
+      <c r="R136" t="s">
+        <v>324</v>
+      </c>
+      <c r="S136" t="s">
+        <v>20</v>
+      </c>
+      <c r="T136">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>475</v>
+      </c>
+      <c r="B137">
+        <v>3371025</v>
+      </c>
+      <c r="C137" t="s">
+        <v>162</v>
+      </c>
+      <c r="D137" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" t="s">
+        <v>163</v>
+      </c>
+      <c r="H137" s="1"/>
+      <c r="L137">
+        <v>1724178</v>
+      </c>
+      <c r="M137" t="s">
+        <v>40</v>
+      </c>
+      <c r="N137" s="2">
         <v>46237</v>
       </c>
-      <c r="O113" s="2">
+      <c r="O137" s="2">
         <v>46237</v>
       </c>
-      <c r="P113">
+      <c r="P137">
         <v>100</v>
       </c>
-      <c r="Q113" t="s">
-        <v>20</v>
-      </c>
-      <c r="R113" t="s">
-        <v>187</v>
-      </c>
-      <c r="S113" t="s">
-        <v>20</v>
-      </c>
-      <c r="T113">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H114" s="1"/>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H115" s="1"/>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H116" s="1"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H117" s="1"/>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H118" s="1"/>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H119" s="1"/>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H120" s="1"/>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H121" s="1"/>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H122" s="1"/>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H123" s="1"/>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H124" s="1"/>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H125" s="1"/>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H126" s="1"/>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H127" s="1"/>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H128" s="1"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-    </row>
-    <row r="129" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H129" s="1"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-    </row>
-    <row r="130" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H130" s="1"/>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-    </row>
-    <row r="131" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H131" s="1"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-    </row>
-    <row r="132" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H132" s="1"/>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-    </row>
-    <row r="133" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H133" s="1"/>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-    </row>
-    <row r="134" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H134" s="1"/>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-    </row>
-    <row r="135" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H135" s="1"/>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-    </row>
-    <row r="136" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H136" s="1"/>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-    </row>
-    <row r="137" spans="8:15" x14ac:dyDescent="0.25">
-      <c r="H137" s="1"/>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-    </row>
-    <row r="138" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="Q137" t="s">
+        <v>20</v>
+      </c>
+      <c r="R137" t="s">
+        <v>164</v>
+      </c>
+      <c r="S137" t="s">
+        <v>20</v>
+      </c>
+      <c r="T137">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>476</v>
+      </c>
+      <c r="B138">
+        <v>3367776</v>
+      </c>
+      <c r="C138" t="s">
+        <v>165</v>
+      </c>
+      <c r="D138" t="s">
+        <v>166</v>
+      </c>
+      <c r="E138" t="s">
+        <v>166</v>
+      </c>
       <c r="H138" s="1"/>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-    </row>
-    <row r="139" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L138">
+        <v>1724178</v>
+      </c>
+      <c r="M138" t="s">
+        <v>40</v>
+      </c>
+      <c r="N138" s="2">
+        <v>46241</v>
+      </c>
+      <c r="O138" s="2">
+        <v>46241</v>
+      </c>
+      <c r="P138">
+        <v>100</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>20</v>
+      </c>
+      <c r="R138" t="s">
+        <v>167</v>
+      </c>
+      <c r="S138" t="s">
+        <v>20</v>
+      </c>
+      <c r="T138">
+        <v>5498</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>478</v>
+      </c>
+      <c r="B139">
+        <v>7364996</v>
+      </c>
+      <c r="C139" t="s">
+        <v>325</v>
+      </c>
+      <c r="D139" t="s">
+        <v>326</v>
+      </c>
+      <c r="E139" t="s">
+        <v>326</v>
+      </c>
       <c r="H139" s="1"/>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-    </row>
-    <row r="140" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L139">
+        <v>1710979</v>
+      </c>
+      <c r="M139" t="s">
+        <v>201</v>
+      </c>
+      <c r="N139" s="2">
+        <v>46303</v>
+      </c>
+      <c r="O139" s="2">
+        <v>46303</v>
+      </c>
+      <c r="P139">
+        <v>92</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>20</v>
+      </c>
+      <c r="R139" t="s">
+        <v>327</v>
+      </c>
+      <c r="S139" t="s">
+        <v>20</v>
+      </c>
+      <c r="T139">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>479</v>
+      </c>
+      <c r="B140">
+        <v>7364996</v>
+      </c>
+      <c r="C140" t="s">
+        <v>325</v>
+      </c>
+      <c r="D140" t="s">
+        <v>326</v>
+      </c>
+      <c r="E140" t="s">
+        <v>326</v>
+      </c>
       <c r="H140" s="1"/>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-    </row>
-    <row r="141" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L140">
+        <v>1706681</v>
+      </c>
+      <c r="M140" t="s">
+        <v>170</v>
+      </c>
+      <c r="N140" s="2">
+        <v>46303</v>
+      </c>
+      <c r="O140" s="2">
+        <v>46303</v>
+      </c>
+      <c r="P140">
+        <v>100</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>20</v>
+      </c>
+      <c r="R140" t="s">
+        <v>328</v>
+      </c>
+      <c r="S140" t="s">
+        <v>20</v>
+      </c>
+      <c r="T140">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>480</v>
+      </c>
+      <c r="B141">
+        <v>7364996</v>
+      </c>
+      <c r="C141" t="s">
+        <v>325</v>
+      </c>
+      <c r="D141" t="s">
+        <v>326</v>
+      </c>
+      <c r="E141" t="s">
+        <v>326</v>
+      </c>
       <c r="H141" s="1"/>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-    </row>
-    <row r="142" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L141">
+        <v>1708464</v>
+      </c>
+      <c r="M141" t="s">
+        <v>194</v>
+      </c>
+      <c r="N141" s="2">
+        <v>46302</v>
+      </c>
+      <c r="O141" s="2">
+        <v>46302</v>
+      </c>
+      <c r="P141">
+        <v>90</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>20</v>
+      </c>
+      <c r="R141" t="s">
+        <v>329</v>
+      </c>
+      <c r="S141" t="s">
+        <v>20</v>
+      </c>
+      <c r="T141">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>481</v>
+      </c>
+      <c r="B142">
+        <v>7364996</v>
+      </c>
+      <c r="C142" t="s">
+        <v>325</v>
+      </c>
+      <c r="D142" t="s">
+        <v>326</v>
+      </c>
+      <c r="E142" t="s">
+        <v>326</v>
+      </c>
       <c r="H142" s="1"/>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-    </row>
-    <row r="143" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="L142">
+        <v>1711329</v>
+      </c>
+      <c r="M142" t="s">
+        <v>203</v>
+      </c>
+      <c r="N142" s="2">
+        <v>46302</v>
+      </c>
+      <c r="O142" s="2">
+        <v>46302</v>
+      </c>
+      <c r="P142">
+        <v>100</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>20</v>
+      </c>
+      <c r="R142" t="s">
+        <v>330</v>
+      </c>
+      <c r="S142" t="s">
+        <v>20</v>
+      </c>
+      <c r="T142">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>485</v>
+      </c>
+      <c r="B143">
+        <v>7031897</v>
+      </c>
+      <c r="C143" t="s">
+        <v>26</v>
+      </c>
+      <c r="D143" t="s">
+        <v>27</v>
+      </c>
+      <c r="E143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G143" t="s">
+        <v>28</v>
+      </c>
       <c r="H143" s="1"/>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
-    </row>
-    <row r="144" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J143" t="s">
+        <v>29</v>
+      </c>
+      <c r="L143">
+        <v>1706681</v>
+      </c>
+      <c r="M143" t="s">
+        <v>170</v>
+      </c>
+      <c r="N143" s="2">
+        <v>46218</v>
+      </c>
+      <c r="O143" s="2">
+        <v>46218</v>
+      </c>
+      <c r="P143">
+        <v>83</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>20</v>
+      </c>
+      <c r="R143" t="s">
+        <v>331</v>
+      </c>
+      <c r="S143" t="s">
+        <v>20</v>
+      </c>
+      <c r="T143">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>486</v>
+      </c>
+      <c r="B144">
+        <v>7031897</v>
+      </c>
+      <c r="C144" t="s">
+        <v>26</v>
+      </c>
+      <c r="D144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G144" t="s">
+        <v>28</v>
+      </c>
       <c r="H144" s="1"/>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
-    </row>
-    <row r="145" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J144" t="s">
+        <v>29</v>
+      </c>
+      <c r="L144">
+        <v>1711329</v>
+      </c>
+      <c r="M144" t="s">
+        <v>203</v>
+      </c>
+      <c r="N144" s="2">
+        <v>46213</v>
+      </c>
+      <c r="O144" s="2">
+        <v>46213</v>
+      </c>
+      <c r="P144">
+        <v>90</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>20</v>
+      </c>
+      <c r="R144" t="s">
+        <v>332</v>
+      </c>
+      <c r="S144" t="s">
+        <v>20</v>
+      </c>
+      <c r="T144">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>487</v>
+      </c>
+      <c r="B145">
+        <v>7031897</v>
+      </c>
+      <c r="C145" t="s">
+        <v>26</v>
+      </c>
+      <c r="D145" t="s">
+        <v>27</v>
+      </c>
+      <c r="E145" t="s">
+        <v>27</v>
+      </c>
+      <c r="G145" t="s">
+        <v>28</v>
+      </c>
       <c r="H145" s="1"/>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
-    </row>
-    <row r="146" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J145" t="s">
+        <v>29</v>
+      </c>
+      <c r="L145">
+        <v>1723203</v>
+      </c>
+      <c r="M145" t="s">
+        <v>36</v>
+      </c>
+      <c r="N145" s="2">
+        <v>46237</v>
+      </c>
+      <c r="O145" s="2">
+        <v>46237</v>
+      </c>
+      <c r="P145">
+        <v>100</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>20</v>
+      </c>
+      <c r="R145" t="s">
+        <v>37</v>
+      </c>
+      <c r="S145" t="s">
+        <v>20</v>
+      </c>
+      <c r="T145">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>488</v>
+      </c>
+      <c r="B146">
+        <v>7031897</v>
+      </c>
+      <c r="C146" t="s">
+        <v>26</v>
+      </c>
+      <c r="D146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G146" t="s">
+        <v>28</v>
+      </c>
       <c r="H146" s="1"/>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
-    </row>
-    <row r="147" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J146" t="s">
+        <v>29</v>
+      </c>
+      <c r="L146">
+        <v>1708464</v>
+      </c>
+      <c r="M146" t="s">
+        <v>194</v>
+      </c>
+      <c r="N146" s="2">
+        <v>46211</v>
+      </c>
+      <c r="O146" s="2">
+        <v>46211</v>
+      </c>
+      <c r="P146">
+        <v>70</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>20</v>
+      </c>
+      <c r="R146" t="s">
+        <v>333</v>
+      </c>
+      <c r="S146" t="s">
+        <v>20</v>
+      </c>
+      <c r="T146">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>489</v>
+      </c>
+      <c r="B147">
+        <v>7031897</v>
+      </c>
+      <c r="C147" t="s">
+        <v>26</v>
+      </c>
+      <c r="D147" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147" t="s">
+        <v>27</v>
+      </c>
+      <c r="G147" t="s">
+        <v>28</v>
+      </c>
       <c r="H147" s="1"/>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
-    </row>
-    <row r="148" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J147" t="s">
+        <v>29</v>
+      </c>
+      <c r="L147">
+        <v>1715169</v>
+      </c>
+      <c r="M147" t="s">
+        <v>259</v>
+      </c>
+      <c r="N147" s="2">
+        <v>46217</v>
+      </c>
+      <c r="O147" s="2">
+        <v>46217</v>
+      </c>
+      <c r="P147">
+        <v>50</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>198</v>
+      </c>
+      <c r="R147" t="s">
+        <v>334</v>
+      </c>
+      <c r="S147" t="s">
+        <v>198</v>
+      </c>
+      <c r="T147">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>490</v>
+      </c>
+      <c r="B148">
+        <v>7031897</v>
+      </c>
+      <c r="C148" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148" t="s">
+        <v>27</v>
+      </c>
+      <c r="E148" t="s">
+        <v>27</v>
+      </c>
+      <c r="G148" t="s">
+        <v>28</v>
+      </c>
       <c r="H148" s="1"/>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
-    </row>
-    <row r="149" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J148" t="s">
+        <v>29</v>
+      </c>
+      <c r="L148">
+        <v>1710979</v>
+      </c>
+      <c r="M148" t="s">
+        <v>201</v>
+      </c>
+      <c r="N148" s="2">
+        <v>46216</v>
+      </c>
+      <c r="O148" s="2">
+        <v>46216</v>
+      </c>
+      <c r="P148">
+        <v>100</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>20</v>
+      </c>
+      <c r="R148" t="s">
+        <v>335</v>
+      </c>
+      <c r="S148" t="s">
+        <v>20</v>
+      </c>
+      <c r="T148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>491</v>
+      </c>
+      <c r="B149">
+        <v>7031897</v>
+      </c>
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" t="s">
+        <v>27</v>
+      </c>
+      <c r="E149" t="s">
+        <v>27</v>
+      </c>
+      <c r="G149" t="s">
+        <v>28</v>
+      </c>
       <c r="H149" s="1"/>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
-    </row>
-    <row r="150" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="J149" t="s">
+        <v>29</v>
+      </c>
+      <c r="L149">
+        <v>1715169</v>
+      </c>
+      <c r="M149" t="s">
+        <v>259</v>
+      </c>
+      <c r="N149" s="2">
+        <v>46217</v>
+      </c>
+      <c r="O149" s="2">
+        <v>46217</v>
+      </c>
+      <c r="P149">
+        <v>75</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>20</v>
+      </c>
+      <c r="R149" t="s">
+        <v>334</v>
+      </c>
+      <c r="S149" t="s">
+        <v>20</v>
+      </c>
+      <c r="T149">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H150" s="1"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
     </row>
-    <row r="151" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H151" s="1"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
     </row>
-    <row r="152" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H152" s="1"/>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
     </row>
-    <row r="153" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H153" s="1"/>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
     </row>
-    <row r="154" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H154" s="1"/>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
     </row>
-    <row r="155" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H155" s="1"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
     </row>
-    <row r="156" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H156" s="1"/>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
     </row>
-    <row r="157" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H157" s="1"/>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
     </row>
-    <row r="158" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H158" s="1"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
     </row>
-    <row r="159" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H159" s="1"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
     </row>
-    <row r="160" spans="8:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H160" s="1"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
